--- a/Excellent.xlsx
+++ b/Excellent.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Project - Learning\Project - Financials\Project - Excellent\Excellent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A60010F2-9E4F-4FA4-BAEF-9C83F7B40981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F6FEB7C-6097-4A57-8CFA-AD4F2CA37196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="862" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="862" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -74,6 +74,33 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={C2CF4C27-CC88-4AED-A439-B713356409F1}</author>
+    <author>tc={1009532E-AF5E-4475-A3B1-59481A972DBF}</author>
+  </authors>
+  <commentList>
+    <comment ref="B25" authorId="0" shapeId="0" xr:uid="{C2CF4C27-CC88-4AED-A439-B713356409F1}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Used for Annual SWP withdrawal calculation.</t>
+      </text>
+    </comment>
+    <comment ref="C25" authorId="1" shapeId="0" xr:uid="{1009532E-AF5E-4475-A3B1-59481A972DBF}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Used for Annual SWP withdrawal calculation.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
     <author>tc={27C1B6D3-3DEC-49A5-8A83-BEF2369533D2}</author>
   </authors>
   <commentList>
@@ -409,10 +436,10 @@
     <t>*Inflation adjusted price is rounded off with next nearest 1000</t>
   </si>
   <si>
-    <t>Future value of SWP withdrawal</t>
-  </si>
-  <si>
     <t>BASIC INFO</t>
+  </si>
+  <si>
+    <t>Annual SWP withdrawal</t>
   </si>
 </sst>
 </file>
@@ -422,7 +449,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -466,6 +493,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -923,15 +956,6 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="3" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -975,12 +999,26 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -990,55 +1028,6 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <u val="double"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -1462,6 +1451,17 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="B25" dT="2025-08-10T17:44:02.06" personId="{3093248D-1E2F-4DCB-89A3-46C9B522FA53}" id="{C2CF4C27-CC88-4AED-A439-B713356409F1}">
+    <text>Used for Annual SWP withdrawal calculation.</text>
+  </threadedComment>
+  <threadedComment ref="C25" dT="2025-08-10T17:43:09.37" personId="{3093248D-1E2F-4DCB-89A3-46C9B522FA53}" id="{1009532E-AF5E-4475-A3B1-59481A972DBF}">
+    <text>Used for Annual SWP withdrawal calculation.</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="E3" dT="2024-07-23T13:32:28.30" personId="{3093248D-1E2F-4DCB-89A3-46C9B522FA53}" id="{27C1B6D3-3DEC-49A5-8A83-BEF2369533D2}">
     <text>Delete an event from computation? 
 In the respective row, select the cell under "Age" field and press delete key.</text>
@@ -1482,8 +1482,8 @@
     <col min="3" max="3" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.140625" customWidth="1"/>
-    <col min="7" max="7" width="46.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="49.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="25.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="16" bestFit="1" customWidth="1"/>
@@ -1553,19 +1553,19 @@
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B9" s="3">
         <f ca="1">YEAR(TODAY())</f>
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C9" s="4">
         <f ca="1">userAge+1</f>
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="D9" s="5">
         <f>ROUND(userCurrentSavings-userCurrentLiabilities, 0)</f>
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="E9" s="14">
         <f>userAnnualSavings</f>
-        <v>1200000</v>
+        <v>600000</v>
       </c>
       <c r="F9" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C9)</f>
@@ -1576,80 +1576,80 @@
         <v/>
       </c>
       <c r="H9" s="5">
-        <f ca="1">IF(AND($C9&gt;userRetirementAge, SUM($E9, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E9, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
+        <f t="shared" ref="H9:H40" ca="1" si="0">IF(AND($C9&gt;userRetirementAge, SUM($E9, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E9, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
         <v>0</v>
       </c>
       <c r="I9" s="5">
         <f ca="1">$D9+$E9+$F9-$H9</f>
-        <v>6200000</v>
+        <v>1600000</v>
       </c>
       <c r="J9" s="5">
-        <f ca="1">ROUND(IF($C9&gt;=userRetirementAge, IF($I9&gt;0, $I9*annualEffectivePostRetirementROI, 0), IF($I9&gt;0, $I9*annualEffectiveROI, 0)), 0)</f>
-        <v>620000</v>
+        <f t="shared" ref="J9:J40" ca="1" si="1">ROUND(IF($C9&gt;=userRetirementAge, IF($I9&gt;0, $I9*annualEffectivePostRetirementROI, 0), IF($I9&gt;0, $I9*annualEffectiveROI, 0)), 0)</f>
+        <v>192000</v>
       </c>
       <c r="K9" s="6">
-        <f ca="1">ROUND(I9+J9, 0)</f>
-        <v>6820000</v>
+        <f t="shared" ref="K9:K40" ca="1" si="2">ROUND(I9+J9, 0)</f>
+        <v>1792000</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B10" s="3">
-        <f t="shared" ref="B10:B41" ca="1" si="0">B9+1</f>
-        <v>2025</v>
+        <f t="shared" ref="B10:B41" ca="1" si="3">B9+1</f>
+        <v>2026</v>
       </c>
       <c r="C10" s="4">
-        <f t="shared" ref="C10:C41" ca="1" si="1">C9+1</f>
-        <v>58</v>
+        <f t="shared" ref="C10:C41" ca="1" si="4">C9+1</f>
+        <v>35</v>
       </c>
       <c r="D10" s="5">
-        <f ca="1">ROUND(K9, 0)</f>
-        <v>6820000</v>
+        <f t="shared" ref="D10:D41" ca="1" si="5">ROUND(K9, 0)</f>
+        <v>1792000</v>
       </c>
       <c r="E10" s="14">
-        <f ca="1">ROUND(IF($C10&gt;userRetirementAge, IF($D10&gt;0,-FV(annualChangeInSWP, $C10-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E9+E9*(annualIncreaseInSavings)), 0)</f>
-        <v>1260000</v>
+        <f t="shared" ref="E10:E41" ca="1" si="6">ROUND(IF($C10&gt;userRetirementAge, IF($D10&gt;0,-FV(annualChangeInSWP, $C10-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E9+E9*(annualIncreaseInSavings)), 0)</f>
+        <v>630000</v>
       </c>
       <c r="F10" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C10)</f>
-        <v>2000000</v>
+        <v>-521000</v>
       </c>
       <c r="G10" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="G10" ca="1">_xlfn.TEXTJOIN(", ", TRUE, IF('Input-Events'!E$4:E$106=$C10, 'Input-Events'!D$4:D$106, ""))</f>
-        <v>Retirement Corpus, Retirement</v>
+        <v>International Trip</v>
       </c>
       <c r="H10" s="5">
-        <f ca="1">IF(AND($C10&gt;userRetirementAge, SUM($E10, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E10, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="I10" s="5">
-        <f t="shared" ref="I10:I73" ca="1" si="2">$D10+$E10+$F10-$H10</f>
-        <v>10080000</v>
+        <f t="shared" ref="I10:I73" ca="1" si="7">$D10+$E10+$F10-$H10</f>
+        <v>1901000</v>
       </c>
       <c r="J10" s="5">
-        <f ca="1">ROUND(IF($C10&gt;=userRetirementAge, IF($I10&gt;0, $I10*annualEffectivePostRetirementROI, 0), IF($I10&gt;0, $I10*annualEffectiveROI, 0)), 0)</f>
-        <v>806400</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>228120</v>
       </c>
       <c r="K10" s="6">
-        <f ca="1">ROUND(I10+J10, 0)</f>
-        <v>10886400</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>2129120</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B11" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2027</v>
       </c>
       <c r="C11" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>59</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>36</v>
       </c>
       <c r="D11" s="5">
-        <f ca="1">ROUND(K10, 0)</f>
-        <v>10886400</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>2129120</v>
       </c>
       <c r="E11" s="14">
-        <f ca="1">ROUND(IF($C11&gt;userRetirementAge, IF($D11&gt;0,-FV(annualChangeInSWP, $C11-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E10+E10*(annualIncreaseInSavings)), 0)</f>
-        <v>-1373880</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>661500</v>
       </c>
       <c r="F11" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C11)</f>
@@ -1660,38 +1660,38 @@
         <v/>
       </c>
       <c r="H11" s="5">
-        <f ca="1">IF(AND($C11&gt;userRetirementAge, SUM($E11, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E11, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>68610</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
       </c>
       <c r="I11" s="5">
+        <f t="shared" ca="1" si="7"/>
+        <v>2790620</v>
+      </c>
+      <c r="J11" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>334874</v>
+      </c>
+      <c r="K11" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>9443910</v>
-      </c>
-      <c r="J11" s="5">
-        <f ca="1">ROUND(IF($C11&gt;=userRetirementAge, IF($I11&gt;0, $I11*annualEffectivePostRetirementROI, 0), IF($I11&gt;0, $I11*annualEffectiveROI, 0)), 0)</f>
-        <v>755513</v>
-      </c>
-      <c r="K11" s="6">
-        <f ca="1">ROUND(I11+J11, 0)</f>
-        <v>10199423</v>
+        <v>3125494</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2027</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2028</v>
       </c>
       <c r="C12" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>60</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>37</v>
       </c>
       <c r="D12" s="5">
-        <f ca="1">ROUND(K11, 0)</f>
-        <v>10199423</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>3125494</v>
       </c>
       <c r="E12" s="14">
-        <f ca="1">ROUND(IF($C12&gt;userRetirementAge, IF($D12&gt;0,-FV(annualChangeInSWP, $C12-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E11+E11*(annualIncreaseInSavings)), 0)</f>
-        <v>-1387619</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>694575</v>
       </c>
       <c r="F12" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C12)</f>
@@ -1702,80 +1702,80 @@
         <v/>
       </c>
       <c r="H12" s="5">
-        <f ca="1">IF(AND($C12&gt;userRetirementAge, SUM($E12, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E12, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>70327.375</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
       </c>
       <c r="I12" s="5">
+        <f t="shared" ca="1" si="7"/>
+        <v>3820069</v>
+      </c>
+      <c r="J12" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>458408</v>
+      </c>
+      <c r="K12" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>8741476.625</v>
-      </c>
-      <c r="J12" s="5">
-        <f ca="1">ROUND(IF($C12&gt;=userRetirementAge, IF($I12&gt;0, $I12*annualEffectivePostRetirementROI, 0), IF($I12&gt;0, $I12*annualEffectiveROI, 0)), 0)</f>
-        <v>699318</v>
-      </c>
-      <c r="K12" s="6">
-        <f ca="1">ROUND(I12+J12, 0)</f>
-        <v>9440795</v>
+        <v>4278477</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B13" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2028</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2029</v>
       </c>
       <c r="C13" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>61</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>38</v>
       </c>
       <c r="D13" s="5">
-        <f ca="1">ROUND(K12, 0)</f>
-        <v>9440795</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>4278477</v>
       </c>
       <c r="E13" s="14">
-        <f ca="1">ROUND(IF($C13&gt;userRetirementAge, IF($D13&gt;0,-FV(annualChangeInSWP, $C13-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E12+E12*(annualIncreaseInSavings)), 0)</f>
-        <v>-1401495</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>729304</v>
       </c>
       <c r="F13" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C13)</f>
-        <v>0</v>
+        <v>-1277000</v>
       </c>
       <c r="G13" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="G13" ca="1">_xlfn.TEXTJOIN(", ", TRUE, IF('Input-Events'!E$4:E$106=$C13, 'Input-Events'!D$4:D$106, ""))</f>
-        <v/>
+        <v>Car</v>
       </c>
       <c r="H13" s="5">
-        <f ca="1">IF(AND($C13&gt;userRetirementAge, SUM($E13, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E13, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>72061.875</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
       </c>
       <c r="I13" s="5">
+        <f t="shared" ca="1" si="7"/>
+        <v>3730781</v>
+      </c>
+      <c r="J13" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>447694</v>
+      </c>
+      <c r="K13" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>7967238.125</v>
-      </c>
-      <c r="J13" s="5">
-        <f ca="1">ROUND(IF($C13&gt;=userRetirementAge, IF($I13&gt;0, $I13*annualEffectivePostRetirementROI, 0), IF($I13&gt;0, $I13*annualEffectiveROI, 0)), 0)</f>
-        <v>637379</v>
-      </c>
-      <c r="K13" s="6">
-        <f ca="1">ROUND(I13+J13, 0)</f>
-        <v>8604617</v>
+        <v>4178475</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B14" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2029</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2030</v>
       </c>
       <c r="C14" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>62</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>39</v>
       </c>
       <c r="D14" s="5">
-        <f ca="1">ROUND(K13, 0)</f>
-        <v>8604617</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>4178475</v>
       </c>
       <c r="E14" s="14">
-        <f ca="1">ROUND(IF($C14&gt;userRetirementAge, IF($D14&gt;0,-FV(annualChangeInSWP, $C14-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E13+E13*(annualIncreaseInSavings)), 0)</f>
-        <v>-1415510</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>765769</v>
       </c>
       <c r="F14" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C14)</f>
@@ -1786,80 +1786,80 @@
         <v/>
       </c>
       <c r="H14" s="5">
-        <f ca="1">IF(AND($C14&gt;userRetirementAge, SUM($E14, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E14, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>73813.75</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
       </c>
       <c r="I14" s="5">
+        <f t="shared" ca="1" si="7"/>
+        <v>4944244</v>
+      </c>
+      <c r="J14" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>593309</v>
+      </c>
+      <c r="K14" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>7115293.25</v>
-      </c>
-      <c r="J14" s="5">
-        <f ca="1">ROUND(IF($C14&gt;=userRetirementAge, IF($I14&gt;0, $I14*annualEffectivePostRetirementROI, 0), IF($I14&gt;0, $I14*annualEffectiveROI, 0)), 0)</f>
-        <v>569223</v>
-      </c>
-      <c r="K14" s="6">
-        <f ca="1">ROUND(I14+J14, 0)</f>
-        <v>7684516</v>
+        <v>5537553</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B15" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2030</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2031</v>
       </c>
       <c r="C15" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>63</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>40</v>
       </c>
       <c r="D15" s="5">
-        <f ca="1">ROUND(K14, 0)</f>
-        <v>7684516</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>5537553</v>
       </c>
       <c r="E15" s="14">
-        <f ca="1">ROUND(IF($C15&gt;userRetirementAge, IF($D15&gt;0,-FV(annualChangeInSWP, $C15-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E14+E14*(annualIncreaseInSavings)), 0)</f>
-        <v>-1429665</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>804057</v>
       </c>
       <c r="F15" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C15)</f>
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="G15" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="G15" ca="1">_xlfn.TEXTJOIN(", ", TRUE, IF('Input-Events'!E$4:E$106=$C15, 'Input-Events'!D$4:D$106, ""))</f>
-        <v/>
+        <v>Children Education, PPF Maturity, Insurance Maturity</v>
       </c>
       <c r="H15" s="5">
-        <f ca="1">IF(AND($C15&gt;userRetirementAge, SUM($E15, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E15, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>75583.125</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
       </c>
       <c r="I15" s="5">
+        <f t="shared" ca="1" si="7"/>
+        <v>6841610</v>
+      </c>
+      <c r="J15" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>820993</v>
+      </c>
+      <c r="K15" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>6179267.875</v>
-      </c>
-      <c r="J15" s="5">
-        <f ca="1">ROUND(IF($C15&gt;=userRetirementAge, IF($I15&gt;0, $I15*annualEffectivePostRetirementROI, 0), IF($I15&gt;0, $I15*annualEffectiveROI, 0)), 0)</f>
-        <v>494341</v>
-      </c>
-      <c r="K15" s="6">
-        <f ca="1">ROUND(I15+J15, 0)</f>
-        <v>6673609</v>
+        <v>7662603</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B16" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2031</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2032</v>
       </c>
       <c r="C16" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>64</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>41</v>
       </c>
       <c r="D16" s="5">
-        <f ca="1">ROUND(K15, 0)</f>
-        <v>6673609</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>7662603</v>
       </c>
       <c r="E16" s="14">
-        <f ca="1">ROUND(IF($C16&gt;userRetirementAge, IF($D16&gt;0,-FV(annualChangeInSWP, $C16-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E15+E15*(annualIncreaseInSavings)), 0)</f>
-        <v>-1443962</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>844260</v>
       </c>
       <c r="F16" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C16)</f>
@@ -1870,38 +1870,38 @@
         <v/>
       </c>
       <c r="H16" s="5">
-        <f ca="1">IF(AND($C16&gt;userRetirementAge, SUM($E16, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E16, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>77370.25</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
       </c>
       <c r="I16" s="5">
+        <f t="shared" ca="1" si="7"/>
+        <v>8506863</v>
+      </c>
+      <c r="J16" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>1020824</v>
+      </c>
+      <c r="K16" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>5152276.75</v>
-      </c>
-      <c r="J16" s="5">
-        <f ca="1">ROUND(IF($C16&gt;=userRetirementAge, IF($I16&gt;0, $I16*annualEffectivePostRetirementROI, 0), IF($I16&gt;0, $I16*annualEffectiveROI, 0)), 0)</f>
-        <v>412182</v>
-      </c>
-      <c r="K16" s="6">
-        <f ca="1">ROUND(I16+J16, 0)</f>
-        <v>5564459</v>
+        <v>9527687</v>
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2032</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2033</v>
       </c>
       <c r="C17" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>65</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>42</v>
       </c>
       <c r="D17" s="5">
-        <f ca="1">ROUND(K16, 0)</f>
-        <v>5564459</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>9527687</v>
       </c>
       <c r="E17" s="14">
-        <f ca="1">ROUND(IF($C17&gt;userRetirementAge, IF($D17&gt;0,-FV(annualChangeInSWP, $C17-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E16+E16*(annualIncreaseInSavings)), 0)</f>
-        <v>-1458401</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>886473</v>
       </c>
       <c r="F17" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C17)</f>
@@ -1912,38 +1912,38 @@
         <v/>
       </c>
       <c r="H17" s="5">
-        <f ca="1">IF(AND($C17&gt;userRetirementAge, SUM($E17, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E17, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>79175.125</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
       </c>
       <c r="I17" s="5">
+        <f t="shared" ca="1" si="7"/>
+        <v>10414160</v>
+      </c>
+      <c r="J17" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>1249699</v>
+      </c>
+      <c r="K17" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>4026882.875</v>
-      </c>
-      <c r="J17" s="5">
-        <f ca="1">ROUND(IF($C17&gt;=userRetirementAge, IF($I17&gt;0, $I17*annualEffectivePostRetirementROI, 0), IF($I17&gt;0, $I17*annualEffectiveROI, 0)), 0)</f>
-        <v>322151</v>
-      </c>
-      <c r="K17" s="6">
-        <f ca="1">ROUND(I17+J17, 0)</f>
-        <v>4349034</v>
+        <v>11663859</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2033</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2034</v>
       </c>
       <c r="C18" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>66</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>43</v>
       </c>
       <c r="D18" s="5">
-        <f ca="1">ROUND(K17, 0)</f>
-        <v>4349034</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>11663859</v>
       </c>
       <c r="E18" s="14">
-        <f ca="1">ROUND(IF($C18&gt;userRetirementAge, IF($D18&gt;0,-FV(annualChangeInSWP, $C18-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E17+E17*(annualIncreaseInSavings)), 0)</f>
-        <v>-1472985</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>930797</v>
       </c>
       <c r="F18" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C18)</f>
@@ -1954,38 +1954,38 @@
         <v/>
       </c>
       <c r="H18" s="5">
-        <f ca="1">IF(AND($C18&gt;userRetirementAge, SUM($E18, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E18, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>80998.125</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
       </c>
       <c r="I18" s="5">
+        <f t="shared" ca="1" si="7"/>
+        <v>12594656</v>
+      </c>
+      <c r="J18" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>1511359</v>
+      </c>
+      <c r="K18" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>2795050.875</v>
-      </c>
-      <c r="J18" s="5">
-        <f ca="1">ROUND(IF($C18&gt;=userRetirementAge, IF($I18&gt;0, $I18*annualEffectivePostRetirementROI, 0), IF($I18&gt;0, $I18*annualEffectiveROI, 0)), 0)</f>
-        <v>223604</v>
-      </c>
-      <c r="K18" s="6">
-        <f ca="1">ROUND(I18+J18, 0)</f>
-        <v>3018655</v>
+        <v>14106015</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2034</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2035</v>
       </c>
       <c r="C19" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>67</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>44</v>
       </c>
       <c r="D19" s="5">
-        <f ca="1">ROUND(K18, 0)</f>
-        <v>3018655</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>14106015</v>
       </c>
       <c r="E19" s="14">
-        <f ca="1">ROUND(IF($C19&gt;userRetirementAge, IF($D19&gt;0,-FV(annualChangeInSWP, $C19-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E18+E18*(annualIncreaseInSavings)), 0)</f>
-        <v>-1487715</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>977337</v>
       </c>
       <c r="F19" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C19)</f>
@@ -1996,38 +1996,38 @@
         <v/>
       </c>
       <c r="H19" s="5">
-        <f ca="1">IF(AND($C19&gt;userRetirementAge, SUM($E19, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E19, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>82839.375</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
       </c>
       <c r="I19" s="5">
+        <f t="shared" ca="1" si="7"/>
+        <v>15083352</v>
+      </c>
+      <c r="J19" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>1810002</v>
+      </c>
+      <c r="K19" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>1448100.625</v>
-      </c>
-      <c r="J19" s="5">
-        <f ca="1">ROUND(IF($C19&gt;=userRetirementAge, IF($I19&gt;0, $I19*annualEffectivePostRetirementROI, 0), IF($I19&gt;0, $I19*annualEffectiveROI, 0)), 0)</f>
-        <v>115848</v>
-      </c>
-      <c r="K19" s="6">
-        <f ca="1">ROUND(I19+J19, 0)</f>
-        <v>1563949</v>
+        <v>16893354</v>
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2035</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2036</v>
       </c>
       <c r="C20" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>68</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>45</v>
       </c>
       <c r="D20" s="5">
-        <f ca="1">ROUND(K19, 0)</f>
-        <v>1563949</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>16893354</v>
       </c>
       <c r="E20" s="14">
-        <f ca="1">ROUND(IF($C20&gt;userRetirementAge, IF($D20&gt;0,-FV(annualChangeInSWP, $C20-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E19+E19*(annualIncreaseInSavings)), 0)</f>
-        <v>-1502592</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1026204</v>
       </c>
       <c r="F20" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C20)</f>
@@ -2038,38 +2038,38 @@
         <v/>
       </c>
       <c r="H20" s="5">
-        <f ca="1">IF(AND($C20&gt;userRetirementAge, SUM($E20, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E20, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>84699</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
       </c>
       <c r="I20" s="5">
+        <f t="shared" ca="1" si="7"/>
+        <v>17919558</v>
+      </c>
+      <c r="J20" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>2150347</v>
+      </c>
+      <c r="K20" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>-23342</v>
-      </c>
-      <c r="J20" s="5">
-        <f ca="1">ROUND(IF($C20&gt;=userRetirementAge, IF($I20&gt;0, $I20*annualEffectivePostRetirementROI, 0), IF($I20&gt;0, $I20*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="K20" s="6">
-        <f ca="1">ROUND(I20+J20, 0)</f>
-        <v>-23342</v>
+        <v>20069905</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2036</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2037</v>
       </c>
       <c r="C21" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>69</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>46</v>
       </c>
       <c r="D21" s="5">
-        <f ca="1">ROUND(K20, 0)</f>
-        <v>-23342</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>20069905</v>
       </c>
       <c r="E21" s="14">
-        <f ca="1">ROUND(IF($C21&gt;userRetirementAge, IF($D21&gt;0,-FV(annualChangeInSWP, $C21-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E20+E20*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1077514</v>
       </c>
       <c r="F21" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C21)</f>
@@ -2080,38 +2080,38 @@
         <v/>
       </c>
       <c r="H21" s="5">
-        <f ca="1">IF(AND($C21&gt;userRetirementAge, SUM($E21, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E21, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="I21" s="5">
+        <f t="shared" ca="1" si="7"/>
+        <v>21147419</v>
+      </c>
+      <c r="J21" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>2537690</v>
+      </c>
+      <c r="K21" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>-23342</v>
-      </c>
-      <c r="J21" s="5">
-        <f ca="1">ROUND(IF($C21&gt;=userRetirementAge, IF($I21&gt;0, $I21*annualEffectivePostRetirementROI, 0), IF($I21&gt;0, $I21*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="K21" s="6">
-        <f ca="1">ROUND(I21+J21, 0)</f>
-        <v>-23342</v>
+        <v>23685109</v>
       </c>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2037</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2038</v>
       </c>
       <c r="C22" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>70</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>47</v>
       </c>
       <c r="D22" s="5">
-        <f ca="1">ROUND(K21, 0)</f>
-        <v>-23342</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>23685109</v>
       </c>
       <c r="E22" s="14">
-        <f ca="1">ROUND(IF($C22&gt;userRetirementAge, IF($D22&gt;0,-FV(annualChangeInSWP, $C22-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E21+E21*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1131390</v>
       </c>
       <c r="F22" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C22)</f>
@@ -2122,38 +2122,38 @@
         <v/>
       </c>
       <c r="H22" s="5">
-        <f ca="1">IF(AND($C22&gt;userRetirementAge, SUM($E22, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E22, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="I22" s="5">
+        <f t="shared" ca="1" si="7"/>
+        <v>24816499</v>
+      </c>
+      <c r="J22" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>2977980</v>
+      </c>
+      <c r="K22" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>-23342</v>
-      </c>
-      <c r="J22" s="5">
-        <f ca="1">ROUND(IF($C22&gt;=userRetirementAge, IF($I22&gt;0, $I22*annualEffectivePostRetirementROI, 0), IF($I22&gt;0, $I22*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="K22" s="6">
-        <f ca="1">ROUND(I22+J22, 0)</f>
-        <v>-23342</v>
+        <v>27794479</v>
       </c>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2038</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2039</v>
       </c>
       <c r="C23" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>71</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>48</v>
       </c>
       <c r="D23" s="5">
-        <f ca="1">ROUND(K22, 0)</f>
-        <v>-23342</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>27794479</v>
       </c>
       <c r="E23" s="14">
-        <f ca="1">ROUND(IF($C23&gt;userRetirementAge, IF($D23&gt;0,-FV(annualChangeInSWP, $C23-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E22+E22*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1187960</v>
       </c>
       <c r="F23" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C23)</f>
@@ -2164,38 +2164,38 @@
         <v/>
       </c>
       <c r="H23" s="5">
-        <f ca="1">IF(AND($C23&gt;userRetirementAge, SUM($E23, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E23, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="I23" s="5">
+        <f t="shared" ca="1" si="7"/>
+        <v>28982439</v>
+      </c>
+      <c r="J23" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>3477893</v>
+      </c>
+      <c r="K23" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>-23342</v>
-      </c>
-      <c r="J23" s="5">
-        <f ca="1">ROUND(IF($C23&gt;=userRetirementAge, IF($I23&gt;0, $I23*annualEffectivePostRetirementROI, 0), IF($I23&gt;0, $I23*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="K23" s="6">
-        <f ca="1">ROUND(I23+J23, 0)</f>
-        <v>-23342</v>
+        <v>32460332</v>
       </c>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2039</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2040</v>
       </c>
       <c r="C24" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>72</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>49</v>
       </c>
       <c r="D24" s="5">
-        <f ca="1">ROUND(K23, 0)</f>
-        <v>-23342</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>32460332</v>
       </c>
       <c r="E24" s="14">
-        <f ca="1">ROUND(IF($C24&gt;userRetirementAge, IF($D24&gt;0,-FV(annualChangeInSWP, $C24-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E23+E23*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1247358</v>
       </c>
       <c r="F24" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C24)</f>
@@ -2206,80 +2206,80 @@
         <v/>
       </c>
       <c r="H24" s="5">
-        <f ca="1">IF(AND($C24&gt;userRetirementAge, SUM($E24, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E24, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="I24" s="5">
+        <f t="shared" ca="1" si="7"/>
+        <v>33707690</v>
+      </c>
+      <c r="J24" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>4044923</v>
+      </c>
+      <c r="K24" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>-23342</v>
-      </c>
-      <c r="J24" s="5">
-        <f ca="1">ROUND(IF($C24&gt;=userRetirementAge, IF($I24&gt;0, $I24*annualEffectivePostRetirementROI, 0), IF($I24&gt;0, $I24*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="K24" s="6">
-        <f ca="1">ROUND(I24+J24, 0)</f>
-        <v>-23342</v>
+        <v>37752613</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2040</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2041</v>
       </c>
       <c r="C25" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>73</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>50</v>
       </c>
       <c r="D25" s="5">
-        <f ca="1">ROUND(K24, 0)</f>
-        <v>-23342</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>37752613</v>
       </c>
       <c r="E25" s="14">
-        <f ca="1">ROUND(IF($C25&gt;userRetirementAge, IF($D25&gt;0,-FV(annualChangeInSWP, $C25-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E24+E24*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1309726</v>
       </c>
       <c r="F25" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C25)</f>
-        <v>0</v>
+        <v>-8265000</v>
       </c>
       <c r="G25" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="G25" ca="1">_xlfn.TEXTJOIN(", ", TRUE, IF('Input-Events'!E$4:E$106=$C25, 'Input-Events'!D$4:D$106, ""))</f>
-        <v/>
+        <v>Home</v>
       </c>
       <c r="H25" s="5">
-        <f ca="1">IF(AND($C25&gt;userRetirementAge, SUM($E25, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E25, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="I25" s="5">
+        <f t="shared" ca="1" si="7"/>
+        <v>30797339</v>
+      </c>
+      <c r="J25" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>3695681</v>
+      </c>
+      <c r="K25" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>-23342</v>
-      </c>
-      <c r="J25" s="5">
-        <f ca="1">ROUND(IF($C25&gt;=userRetirementAge, IF($I25&gt;0, $I25*annualEffectivePostRetirementROI, 0), IF($I25&gt;0, $I25*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="K25" s="6">
-        <f ca="1">ROUND(I25+J25, 0)</f>
-        <v>-23342</v>
+        <v>34493020</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2041</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2042</v>
       </c>
       <c r="C26" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>74</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>51</v>
       </c>
       <c r="D26" s="5">
-        <f ca="1">ROUND(K25, 0)</f>
-        <v>-23342</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>34493020</v>
       </c>
       <c r="E26" s="14">
-        <f ca="1">ROUND(IF($C26&gt;userRetirementAge, IF($D26&gt;0,-FV(annualChangeInSWP, $C26-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E25+E25*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1375212</v>
       </c>
       <c r="F26" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C26)</f>
@@ -2290,38 +2290,38 @@
         <v/>
       </c>
       <c r="H26" s="5">
-        <f ca="1">IF(AND($C26&gt;userRetirementAge, SUM($E26, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E26, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="I26" s="5">
+        <f t="shared" ca="1" si="7"/>
+        <v>35868232</v>
+      </c>
+      <c r="J26" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>4304188</v>
+      </c>
+      <c r="K26" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>-23342</v>
-      </c>
-      <c r="J26" s="5">
-        <f ca="1">ROUND(IF($C26&gt;=userRetirementAge, IF($I26&gt;0, $I26*annualEffectivePostRetirementROI, 0), IF($I26&gt;0, $I26*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="K26" s="6">
-        <f ca="1">ROUND(I26+J26, 0)</f>
-        <v>-23342</v>
+        <v>40172420</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2042</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2043</v>
       </c>
       <c r="C27" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>75</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>52</v>
       </c>
       <c r="D27" s="5">
-        <f ca="1">ROUND(K26, 0)</f>
-        <v>-23342</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>40172420</v>
       </c>
       <c r="E27" s="14">
-        <f ca="1">ROUND(IF($C27&gt;userRetirementAge, IF($D27&gt;0,-FV(annualChangeInSWP, $C27-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E26+E26*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1443973</v>
       </c>
       <c r="F27" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C27)</f>
@@ -2332,38 +2332,38 @@
         <v/>
       </c>
       <c r="H27" s="5">
-        <f ca="1">IF(AND($C27&gt;userRetirementAge, SUM($E27, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E27, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="I27" s="5">
+        <f t="shared" ca="1" si="7"/>
+        <v>41616393</v>
+      </c>
+      <c r="J27" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>4993967</v>
+      </c>
+      <c r="K27" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>-23342</v>
-      </c>
-      <c r="J27" s="5">
-        <f ca="1">ROUND(IF($C27&gt;=userRetirementAge, IF($I27&gt;0, $I27*annualEffectivePostRetirementROI, 0), IF($I27&gt;0, $I27*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="K27" s="6">
-        <f ca="1">ROUND(I27+J27, 0)</f>
-        <v>-23342</v>
+        <v>46610360</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2043</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2044</v>
       </c>
       <c r="C28" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>76</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>53</v>
       </c>
       <c r="D28" s="5">
-        <f ca="1">ROUND(K27, 0)</f>
-        <v>-23342</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>46610360</v>
       </c>
       <c r="E28" s="14">
-        <f ca="1">ROUND(IF($C28&gt;userRetirementAge, IF($D28&gt;0,-FV(annualChangeInSWP, $C28-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E27+E27*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1516172</v>
       </c>
       <c r="F28" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C28)</f>
@@ -2374,38 +2374,38 @@
         <v/>
       </c>
       <c r="H28" s="5">
-        <f ca="1">IF(AND($C28&gt;userRetirementAge, SUM($E28, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E28, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="I28" s="5">
+        <f t="shared" ca="1" si="7"/>
+        <v>48126532</v>
+      </c>
+      <c r="J28" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>5775184</v>
+      </c>
+      <c r="K28" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>-23342</v>
-      </c>
-      <c r="J28" s="5">
-        <f ca="1">ROUND(IF($C28&gt;=userRetirementAge, IF($I28&gt;0, $I28*annualEffectivePostRetirementROI, 0), IF($I28&gt;0, $I28*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="K28" s="6">
-        <f ca="1">ROUND(I28+J28, 0)</f>
-        <v>-23342</v>
+        <v>53901716</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2044</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2045</v>
       </c>
       <c r="C29" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>77</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>54</v>
       </c>
       <c r="D29" s="5">
-        <f ca="1">ROUND(K28, 0)</f>
-        <v>-23342</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>53901716</v>
       </c>
       <c r="E29" s="14">
-        <f ca="1">ROUND(IF($C29&gt;userRetirementAge, IF($D29&gt;0,-FV(annualChangeInSWP, $C29-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E28+E28*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1591981</v>
       </c>
       <c r="F29" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C29)</f>
@@ -2416,38 +2416,38 @@
         <v/>
       </c>
       <c r="H29" s="5">
-        <f ca="1">IF(AND($C29&gt;userRetirementAge, SUM($E29, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E29, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="I29" s="5">
+        <f t="shared" ca="1" si="7"/>
+        <v>55493697</v>
+      </c>
+      <c r="J29" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>6659244</v>
+      </c>
+      <c r="K29" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>-23342</v>
-      </c>
-      <c r="J29" s="5">
-        <f ca="1">ROUND(IF($C29&gt;=userRetirementAge, IF($I29&gt;0, $I29*annualEffectivePostRetirementROI, 0), IF($I29&gt;0, $I29*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="K29" s="6">
-        <f ca="1">ROUND(I29+J29, 0)</f>
-        <v>-23342</v>
+        <v>62152941</v>
       </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2045</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2046</v>
       </c>
       <c r="C30" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>78</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>55</v>
       </c>
       <c r="D30" s="5">
-        <f ca="1">ROUND(K29, 0)</f>
-        <v>-23342</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>62152941</v>
       </c>
       <c r="E30" s="14">
-        <f ca="1">ROUND(IF($C30&gt;userRetirementAge, IF($D30&gt;0,-FV(annualChangeInSWP, $C30-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E29+E29*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1671580</v>
       </c>
       <c r="F30" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C30)</f>
@@ -2458,38 +2458,38 @@
         <v/>
       </c>
       <c r="H30" s="5">
-        <f ca="1">IF(AND($C30&gt;userRetirementAge, SUM($E30, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E30, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="I30" s="5">
+        <f t="shared" ca="1" si="7"/>
+        <v>63824521</v>
+      </c>
+      <c r="J30" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>7658943</v>
+      </c>
+      <c r="K30" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>-23342</v>
-      </c>
-      <c r="J30" s="5">
-        <f ca="1">ROUND(IF($C30&gt;=userRetirementAge, IF($I30&gt;0, $I30*annualEffectivePostRetirementROI, 0), IF($I30&gt;0, $I30*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="K30" s="6">
-        <f ca="1">ROUND(I30+J30, 0)</f>
-        <v>-23342</v>
+        <v>71483464</v>
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2046</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2047</v>
       </c>
       <c r="C31" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>79</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>56</v>
       </c>
       <c r="D31" s="5">
-        <f ca="1">ROUND(K30, 0)</f>
-        <v>-23342</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>71483464</v>
       </c>
       <c r="E31" s="14">
-        <f ca="1">ROUND(IF($C31&gt;userRetirementAge, IF($D31&gt;0,-FV(annualChangeInSWP, $C31-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E30+E30*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1755159</v>
       </c>
       <c r="F31" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C31)</f>
@@ -2500,80 +2500,80 @@
         <v/>
       </c>
       <c r="H31" s="5">
-        <f ca="1">IF(AND($C31&gt;userRetirementAge, SUM($E31, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E31, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="I31" s="5">
+        <f t="shared" ca="1" si="7"/>
+        <v>73238623</v>
+      </c>
+      <c r="J31" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>8788635</v>
+      </c>
+      <c r="K31" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>-23342</v>
-      </c>
-      <c r="J31" s="5">
-        <f ca="1">ROUND(IF($C31&gt;=userRetirementAge, IF($I31&gt;0, $I31*annualEffectivePostRetirementROI, 0), IF($I31&gt;0, $I31*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="K31" s="6">
-        <f ca="1">ROUND(I31+J31, 0)</f>
-        <v>-23342</v>
+        <v>82027258</v>
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2047</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2048</v>
       </c>
       <c r="C32" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>80</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>57</v>
       </c>
       <c r="D32" s="5">
-        <f ca="1">ROUND(K31, 0)</f>
-        <v>-23342</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>82027258</v>
       </c>
       <c r="E32" s="14">
-        <f ca="1">ROUND(IF($C32&gt;userRetirementAge, IF($D32&gt;0,-FV(annualChangeInSWP, $C32-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E31+E31*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1842917</v>
       </c>
       <c r="F32" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C32)</f>
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="G32" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="G32" ca="1">_xlfn.TEXTJOIN(", ", TRUE, IF('Input-Events'!E$4:E$106=$C32, 'Input-Events'!D$4:D$106, ""))</f>
-        <v>Term Insurance, Life Expectancy</v>
+        <v/>
       </c>
       <c r="H32" s="5">
-        <f ca="1">IF(AND($C32&gt;userRetirementAge, SUM($E32, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E32, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="I32" s="5">
+        <f t="shared" ca="1" si="7"/>
+        <v>83870175</v>
+      </c>
+      <c r="J32" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>10064421</v>
+      </c>
+      <c r="K32" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>9976658</v>
-      </c>
-      <c r="J32" s="5">
-        <f ca="1">ROUND(IF($C32&gt;=userRetirementAge, IF($I32&gt;0, $I32*annualEffectivePostRetirementROI, 0), IF($I32&gt;0, $I32*annualEffectiveROI, 0)), 0)</f>
-        <v>798133</v>
-      </c>
-      <c r="K32" s="6">
-        <f ca="1">ROUND(I32+J32, 0)</f>
-        <v>10774791</v>
+        <v>93934596</v>
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2048</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2049</v>
       </c>
       <c r="C33" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>81</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>58</v>
       </c>
       <c r="D33" s="5">
-        <f ca="1">ROUND(K32, 0)</f>
-        <v>10774791</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>93934596</v>
       </c>
       <c r="E33" s="14">
-        <f ca="1">ROUND(IF($C33&gt;userRetirementAge, IF($D33&gt;0,-FV(annualChangeInSWP, $C33-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E32+E32*(annualIncreaseInSavings)), 0)</f>
-        <v>-1710090</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1935063</v>
       </c>
       <c r="F33" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C33)</f>
@@ -2584,38 +2584,38 @@
         <v/>
       </c>
       <c r="H33" s="5">
-        <f ca="1">IF(AND($C33&gt;userRetirementAge, SUM($E33, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E33, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>110636.25</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
       </c>
       <c r="I33" s="5">
+        <f t="shared" ca="1" si="7"/>
+        <v>95869659</v>
+      </c>
+      <c r="J33" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>11504359</v>
+      </c>
+      <c r="K33" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>8954064.75</v>
-      </c>
-      <c r="J33" s="5">
-        <f ca="1">ROUND(IF($C33&gt;=userRetirementAge, IF($I33&gt;0, $I33*annualEffectivePostRetirementROI, 0), IF($I33&gt;0, $I33*annualEffectiveROI, 0)), 0)</f>
-        <v>716325</v>
-      </c>
-      <c r="K33" s="6">
-        <f ca="1">ROUND(I33+J33, 0)</f>
-        <v>9670390</v>
+        <v>107374018</v>
       </c>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2049</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2050</v>
       </c>
       <c r="C34" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>82</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>59</v>
       </c>
       <c r="D34" s="5">
-        <f ca="1">ROUND(K33, 0)</f>
-        <v>9670390</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>107374018</v>
       </c>
       <c r="E34" s="14">
-        <f ca="1">ROUND(IF($C34&gt;userRetirementAge, IF($D34&gt;0,-FV(annualChangeInSWP, $C34-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E33+E33*(annualIncreaseInSavings)), 0)</f>
-        <v>-1727191</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>2031816</v>
       </c>
       <c r="F34" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C34)</f>
@@ -2626,80 +2626,80 @@
         <v/>
       </c>
       <c r="H34" s="5">
-        <f ca="1">IF(AND($C34&gt;userRetirementAge, SUM($E34, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E34, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>112773.875</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
       </c>
       <c r="I34" s="5">
+        <f t="shared" ca="1" si="7"/>
+        <v>109405834</v>
+      </c>
+      <c r="J34" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>13128700</v>
+      </c>
+      <c r="K34" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>7830425.125</v>
-      </c>
-      <c r="J34" s="5">
-        <f ca="1">ROUND(IF($C34&gt;=userRetirementAge, IF($I34&gt;0, $I34*annualEffectivePostRetirementROI, 0), IF($I34&gt;0, $I34*annualEffectiveROI, 0)), 0)</f>
-        <v>626434</v>
-      </c>
-      <c r="K34" s="6">
-        <f ca="1">ROUND(I34+J34, 0)</f>
-        <v>8456859</v>
+        <v>122534534</v>
       </c>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2050</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2051</v>
       </c>
       <c r="C35" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>83</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>60</v>
       </c>
       <c r="D35" s="5">
-        <f ca="1">ROUND(K34, 0)</f>
-        <v>8456859</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>122534534</v>
       </c>
       <c r="E35" s="14">
-        <f ca="1">ROUND(IF($C35&gt;userRetirementAge, IF($D35&gt;0,-FV(annualChangeInSWP, $C35-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E34+E34*(annualIncreaseInSavings)), 0)</f>
-        <v>-1744463</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>2133407</v>
       </c>
       <c r="F35" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C35)</f>
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="G35" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="G35" ca="1">_xlfn.TEXTJOIN(", ", TRUE, IF('Input-Events'!E$4:E$106=$C35, 'Input-Events'!D$4:D$106, ""))</f>
-        <v/>
+        <v>Retirement Corpus, Retirement</v>
       </c>
       <c r="H35" s="5">
-        <f ca="1">IF(AND($C35&gt;userRetirementAge, SUM($E35, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E35, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>114932.875</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
       </c>
       <c r="I35" s="5">
+        <f t="shared" ca="1" si="7"/>
+        <v>126667941</v>
+      </c>
+      <c r="J35" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>15200153</v>
+      </c>
+      <c r="K35" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>6597463.125</v>
-      </c>
-      <c r="J35" s="5">
-        <f ca="1">ROUND(IF($C35&gt;=userRetirementAge, IF($I35&gt;0, $I35*annualEffectivePostRetirementROI, 0), IF($I35&gt;0, $I35*annualEffectiveROI, 0)), 0)</f>
-        <v>527797</v>
-      </c>
-      <c r="K35" s="6">
-        <f ca="1">ROUND(I35+J35, 0)</f>
-        <v>7125260</v>
+        <v>141868094</v>
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2051</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2052</v>
       </c>
       <c r="C36" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>84</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>61</v>
       </c>
       <c r="D36" s="5">
-        <f ca="1">ROUND(K35, 0)</f>
-        <v>7125260</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>141868094</v>
       </c>
       <c r="E36" s="14">
-        <f ca="1">ROUND(IF($C36&gt;userRetirementAge, IF($D36&gt;0,-FV(annualChangeInSWP, $C36-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E35+E35*(annualIncreaseInSavings)), 0)</f>
-        <v>-1761908</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-4480148</v>
       </c>
       <c r="F36" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C36)</f>
@@ -2710,38 +2710,38 @@
         <v/>
       </c>
       <c r="H36" s="5">
-        <f ca="1">IF(AND($C36&gt;userRetirementAge, SUM($E36, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E36, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>117113.5</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>394393.5</v>
       </c>
       <c r="I36" s="5">
+        <f t="shared" ca="1" si="7"/>
+        <v>136993552.5</v>
+      </c>
+      <c r="J36" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>16439226</v>
+      </c>
+      <c r="K36" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>5246238.5</v>
-      </c>
-      <c r="J36" s="5">
-        <f ca="1">ROUND(IF($C36&gt;=userRetirementAge, IF($I36&gt;0, $I36*annualEffectivePostRetirementROI, 0), IF($I36&gt;0, $I36*annualEffectiveROI, 0)), 0)</f>
-        <v>419699</v>
-      </c>
-      <c r="K36" s="6">
-        <f ca="1">ROUND(I36+J36, 0)</f>
-        <v>5665938</v>
+        <v>153432779</v>
       </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2052</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2053</v>
       </c>
       <c r="C37" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>85</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>62</v>
       </c>
       <c r="D37" s="5">
-        <f ca="1">ROUND(K36, 0)</f>
-        <v>5665938</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>153432779</v>
       </c>
       <c r="E37" s="14">
-        <f ca="1">ROUND(IF($C37&gt;userRetirementAge, IF($D37&gt;0,-FV(annualChangeInSWP, $C37-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E36+E36*(annualIncreaseInSavings)), 0)</f>
-        <v>-1779527</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-4524949</v>
       </c>
       <c r="F37" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C37)</f>
@@ -2752,38 +2752,38 @@
         <v/>
       </c>
       <c r="H37" s="5">
-        <f ca="1">IF(AND($C37&gt;userRetirementAge, SUM($E37, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E37, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>119315.875</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>399993.625</v>
       </c>
       <c r="I37" s="5">
+        <f t="shared" ca="1" si="7"/>
+        <v>148507836.375</v>
+      </c>
+      <c r="J37" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>17820940</v>
+      </c>
+      <c r="K37" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>3767095.125</v>
-      </c>
-      <c r="J37" s="5">
-        <f ca="1">ROUND(IF($C37&gt;=userRetirementAge, IF($I37&gt;0, $I37*annualEffectivePostRetirementROI, 0), IF($I37&gt;0, $I37*annualEffectiveROI, 0)), 0)</f>
-        <v>301368</v>
-      </c>
-      <c r="K37" s="6">
-        <f ca="1">ROUND(I37+J37, 0)</f>
-        <v>4068463</v>
+        <v>166328776</v>
       </c>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2053</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2054</v>
       </c>
       <c r="C38" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>86</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>63</v>
       </c>
       <c r="D38" s="5">
-        <f ca="1">ROUND(K37, 0)</f>
-        <v>4068463</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>166328776</v>
       </c>
       <c r="E38" s="14">
-        <f ca="1">ROUND(IF($C38&gt;userRetirementAge, IF($D38&gt;0,-FV(annualChangeInSWP, $C38-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E37+E37*(annualIncreaseInSavings)), 0)</f>
-        <v>-1797322</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-4570199</v>
       </c>
       <c r="F38" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C38)</f>
@@ -2794,38 +2794,38 @@
         <v/>
       </c>
       <c r="H38" s="5">
-        <f ca="1">IF(AND($C38&gt;userRetirementAge, SUM($E38, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E38, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>121540.25</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>405649.875</v>
       </c>
       <c r="I38" s="5">
+        <f t="shared" ca="1" si="7"/>
+        <v>161352927.125</v>
+      </c>
+      <c r="J38" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>19362351</v>
+      </c>
+      <c r="K38" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>2149600.75</v>
-      </c>
-      <c r="J38" s="5">
-        <f ca="1">ROUND(IF($C38&gt;=userRetirementAge, IF($I38&gt;0, $I38*annualEffectivePostRetirementROI, 0), IF($I38&gt;0, $I38*annualEffectiveROI, 0)), 0)</f>
-        <v>171968</v>
-      </c>
-      <c r="K38" s="6">
-        <f ca="1">ROUND(I38+J38, 0)</f>
-        <v>2321569</v>
+        <v>180715278</v>
       </c>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2054</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2055</v>
       </c>
       <c r="C39" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>87</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>64</v>
       </c>
       <c r="D39" s="5">
-        <f ca="1">ROUND(K38, 0)</f>
-        <v>2321569</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>180715278</v>
       </c>
       <c r="E39" s="14">
-        <f ca="1">ROUND(IF($C39&gt;userRetirementAge, IF($D39&gt;0,-FV(annualChangeInSWP, $C39-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E38+E38*(annualIncreaseInSavings)), 0)</f>
-        <v>-1815295</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-4615901</v>
       </c>
       <c r="F39" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C39)</f>
@@ -2836,38 +2836,38 @@
         <v/>
       </c>
       <c r="H39" s="5">
-        <f ca="1">IF(AND($C39&gt;userRetirementAge, SUM($E39, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E39, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>123786.875</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>411362.625</v>
       </c>
       <c r="I39" s="5">
+        <f t="shared" ca="1" si="7"/>
+        <v>175688014.375</v>
+      </c>
+      <c r="J39" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>21082562</v>
+      </c>
+      <c r="K39" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>382487.125</v>
-      </c>
-      <c r="J39" s="5">
-        <f ca="1">ROUND(IF($C39&gt;=userRetirementAge, IF($I39&gt;0, $I39*annualEffectivePostRetirementROI, 0), IF($I39&gt;0, $I39*annualEffectiveROI, 0)), 0)</f>
-        <v>30599</v>
-      </c>
-      <c r="K39" s="6">
-        <f ca="1">ROUND(I39+J39, 0)</f>
-        <v>413086</v>
+        <v>196770576</v>
       </c>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2055</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2056</v>
       </c>
       <c r="C40" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>88</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>65</v>
       </c>
       <c r="D40" s="5">
-        <f ca="1">ROUND(K39, 0)</f>
-        <v>413086</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>196770576</v>
       </c>
       <c r="E40" s="14">
-        <f ca="1">ROUND(IF($C40&gt;userRetirementAge, IF($D40&gt;0,-FV(annualChangeInSWP, $C40-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E39+E39*(annualIncreaseInSavings)), 0)</f>
-        <v>-1833448</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-4662060</v>
       </c>
       <c r="F40" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C40)</f>
@@ -2878,38 +2878,38 @@
         <v/>
       </c>
       <c r="H40" s="5">
-        <f ca="1">IF(AND($C40&gt;userRetirementAge, SUM($E40, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E40, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>126056</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>417132.5</v>
       </c>
       <c r="I40" s="5">
+        <f t="shared" ca="1" si="7"/>
+        <v>191691383.5</v>
+      </c>
+      <c r="J40" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>23002966</v>
+      </c>
+      <c r="K40" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
-      </c>
-      <c r="J40" s="5">
-        <f ca="1">ROUND(IF($C40&gt;=userRetirementAge, IF($I40&gt;0, $I40*annualEffectivePostRetirementROI, 0), IF($I40&gt;0, $I40*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="K40" s="6">
-        <f ca="1">ROUND(I40+J40, 0)</f>
-        <v>-1546418</v>
+        <v>214694350</v>
       </c>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2056</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2057</v>
       </c>
       <c r="C41" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>89</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>66</v>
       </c>
       <c r="D41" s="5">
-        <f ca="1">ROUND(K40, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>214694350</v>
       </c>
       <c r="E41" s="14">
-        <f ca="1">ROUND(IF($C41&gt;userRetirementAge, IF($D41&gt;0,-FV(annualChangeInSWP, $C41-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E40+E40*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-4708681</v>
       </c>
       <c r="F41" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C41)</f>
@@ -2920,38 +2920,38 @@
         <v/>
       </c>
       <c r="H41" s="5">
-        <f ca="1">IF(AND($C41&gt;userRetirementAge, SUM($E41, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E41, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ref="H41:H72" ca="1" si="8">IF(AND($C41&gt;userRetirementAge, SUM($E41, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E41, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
+        <v>422960.125</v>
       </c>
       <c r="I41" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>209562708.875</v>
       </c>
       <c r="J41" s="5">
-        <f ca="1">ROUND(IF($C41&gt;=userRetirementAge, IF($I41&gt;0, $I41*annualEffectivePostRetirementROI, 0), IF($I41&gt;0, $I41*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ref="J41:J72" ca="1" si="9">ROUND(IF($C41&gt;=userRetirementAge, IF($I41&gt;0, $I41*annualEffectivePostRetirementROI, 0), IF($I41&gt;0, $I41*annualEffectiveROI, 0)), 0)</f>
+        <v>25147525</v>
       </c>
       <c r="K41" s="6">
-        <f ca="1">ROUND(I41+J41, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ref="K41:K72" ca="1" si="10">ROUND(I41+J41, 0)</f>
+        <v>234710234</v>
       </c>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="3">
-        <f t="shared" ref="B42:B73" ca="1" si="3">B41+1</f>
-        <v>2057</v>
+        <f t="shared" ref="B42:B73" ca="1" si="11">B41+1</f>
+        <v>2058</v>
       </c>
       <c r="C42" s="4">
-        <f t="shared" ref="C42:C73" ca="1" si="4">C41+1</f>
-        <v>90</v>
+        <f t="shared" ref="C42:C73" ca="1" si="12">C41+1</f>
+        <v>67</v>
       </c>
       <c r="D42" s="5">
-        <f ca="1">ROUND(K41, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ref="D42:D73" ca="1" si="13">ROUND(K41, 0)</f>
+        <v>234710234</v>
       </c>
       <c r="E42" s="14">
-        <f ca="1">ROUND(IF($C42&gt;userRetirementAge, IF($D42&gt;0,-FV(annualChangeInSWP, $C42-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E41+E41*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ref="E42:E73" ca="1" si="14">ROUND(IF($C42&gt;userRetirementAge, IF($D42&gt;0,-FV(annualChangeInSWP, $C42-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E41+E41*(annualIncreaseInSavings)), 0)</f>
+        <v>-4755767</v>
       </c>
       <c r="F42" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C42)</f>
@@ -2962,38 +2962,38 @@
         <v/>
       </c>
       <c r="H42" s="5">
-        <f ca="1">IF(AND($C42&gt;userRetirementAge, SUM($E42, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E42, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>428845.875</v>
       </c>
       <c r="I42" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>229525621.125</v>
       </c>
       <c r="J42" s="5">
-        <f ca="1">ROUND(IF($C42&gt;=userRetirementAge, IF($I42&gt;0, $I42*annualEffectivePostRetirementROI, 0), IF($I42&gt;0, $I42*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>27543075</v>
       </c>
       <c r="K42" s="6">
-        <f ca="1">ROUND(I42+J42, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>257068696</v>
       </c>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2058</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2059</v>
       </c>
       <c r="C43" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>91</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>68</v>
       </c>
       <c r="D43" s="5">
-        <f ca="1">ROUND(K42, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>257068696</v>
       </c>
       <c r="E43" s="14">
-        <f ca="1">ROUND(IF($C43&gt;userRetirementAge, IF($D43&gt;0,-FV(annualChangeInSWP, $C43-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E42+E42*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-4803325</v>
       </c>
       <c r="F43" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C43)</f>
@@ -3004,38 +3004,38 @@
         <v/>
       </c>
       <c r="H43" s="5">
-        <f ca="1">IF(AND($C43&gt;userRetirementAge, SUM($E43, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E43, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>434790.625</v>
       </c>
       <c r="I43" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>251830580.375</v>
       </c>
       <c r="J43" s="5">
-        <f ca="1">ROUND(IF($C43&gt;=userRetirementAge, IF($I43&gt;0, $I43*annualEffectivePostRetirementROI, 0), IF($I43&gt;0, $I43*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>30219670</v>
       </c>
       <c r="K43" s="6">
-        <f ca="1">ROUND(I43+J43, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>282050250</v>
       </c>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2059</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2060</v>
       </c>
       <c r="C44" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>92</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>69</v>
       </c>
       <c r="D44" s="5">
-        <f ca="1">ROUND(K43, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>282050250</v>
       </c>
       <c r="E44" s="14">
-        <f ca="1">ROUND(IF($C44&gt;userRetirementAge, IF($D44&gt;0,-FV(annualChangeInSWP, $C44-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E43+E43*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-4851358</v>
       </c>
       <c r="F44" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C44)</f>
@@ -3046,38 +3046,38 @@
         <v/>
       </c>
       <c r="H44" s="5">
-        <f ca="1">IF(AND($C44&gt;userRetirementAge, SUM($E44, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E44, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>440794.75</v>
       </c>
       <c r="I44" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>276758097.25</v>
       </c>
       <c r="J44" s="5">
-        <f ca="1">ROUND(IF($C44&gt;=userRetirementAge, IF($I44&gt;0, $I44*annualEffectivePostRetirementROI, 0), IF($I44&gt;0, $I44*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>33210972</v>
       </c>
       <c r="K44" s="6">
-        <f ca="1">ROUND(I44+J44, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>309969069</v>
       </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2060</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2061</v>
       </c>
       <c r="C45" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>93</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>70</v>
       </c>
       <c r="D45" s="5">
-        <f ca="1">ROUND(K44, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>309969069</v>
       </c>
       <c r="E45" s="14">
-        <f ca="1">ROUND(IF($C45&gt;userRetirementAge, IF($D45&gt;0,-FV(annualChangeInSWP, $C45-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E44+E44*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-4899872</v>
       </c>
       <c r="F45" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C45)</f>
@@ -3088,38 +3088,38 @@
         <v/>
       </c>
       <c r="H45" s="5">
-        <f ca="1">IF(AND($C45&gt;userRetirementAge, SUM($E45, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E45, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>446859</v>
       </c>
       <c r="I45" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>304622338</v>
       </c>
       <c r="J45" s="5">
-        <f ca="1">ROUND(IF($C45&gt;=userRetirementAge, IF($I45&gt;0, $I45*annualEffectivePostRetirementROI, 0), IF($I45&gt;0, $I45*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>36554681</v>
       </c>
       <c r="K45" s="6">
-        <f ca="1">ROUND(I45+J45, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>341177019</v>
       </c>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2061</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2062</v>
       </c>
       <c r="C46" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>94</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>71</v>
       </c>
       <c r="D46" s="5">
-        <f ca="1">ROUND(K45, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>341177019</v>
       </c>
       <c r="E46" s="14">
-        <f ca="1">ROUND(IF($C46&gt;userRetirementAge, IF($D46&gt;0,-FV(annualChangeInSWP, $C46-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E45+E45*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-4948871</v>
       </c>
       <c r="F46" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C46)</f>
@@ -3130,38 +3130,38 @@
         <v/>
       </c>
       <c r="H46" s="5">
-        <f ca="1">IF(AND($C46&gt;userRetirementAge, SUM($E46, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E46, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>452983.875</v>
       </c>
       <c r="I46" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>335775164.125</v>
       </c>
       <c r="J46" s="5">
-        <f ca="1">ROUND(IF($C46&gt;=userRetirementAge, IF($I46&gt;0, $I46*annualEffectivePostRetirementROI, 0), IF($I46&gt;0, $I46*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>40293020</v>
       </c>
       <c r="K46" s="6">
-        <f ca="1">ROUND(I46+J46, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>376068184</v>
       </c>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B47" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2062</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2063</v>
       </c>
       <c r="C47" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>95</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>72</v>
       </c>
       <c r="D47" s="5">
-        <f ca="1">ROUND(K46, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>376068184</v>
       </c>
       <c r="E47" s="14">
-        <f ca="1">ROUND(IF($C47&gt;userRetirementAge, IF($D47&gt;0,-FV(annualChangeInSWP, $C47-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E46+E46*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-4998359</v>
       </c>
       <c r="F47" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C47)</f>
@@ -3172,38 +3172,38 @@
         <v/>
       </c>
       <c r="H47" s="5">
-        <f ca="1">IF(AND($C47&gt;userRetirementAge, SUM($E47, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E47, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>459169.875</v>
       </c>
       <c r="I47" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>370610655.125</v>
       </c>
       <c r="J47" s="5">
-        <f ca="1">ROUND(IF($C47&gt;=userRetirementAge, IF($I47&gt;0, $I47*annualEffectivePostRetirementROI, 0), IF($I47&gt;0, $I47*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>44473279</v>
       </c>
       <c r="K47" s="6">
-        <f ca="1">ROUND(I47+J47, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>415083934</v>
       </c>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2063</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2064</v>
       </c>
       <c r="C48" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>96</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>73</v>
       </c>
       <c r="D48" s="5">
-        <f ca="1">ROUND(K47, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>415083934</v>
       </c>
       <c r="E48" s="14">
-        <f ca="1">ROUND(IF($C48&gt;userRetirementAge, IF($D48&gt;0,-FV(annualChangeInSWP, $C48-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E47+E47*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-5048343</v>
       </c>
       <c r="F48" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C48)</f>
@@ -3214,38 +3214,38 @@
         <v/>
       </c>
       <c r="H48" s="5">
-        <f ca="1">IF(AND($C48&gt;userRetirementAge, SUM($E48, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E48, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>465417.875</v>
       </c>
       <c r="I48" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>409570173.125</v>
       </c>
       <c r="J48" s="5">
-        <f ca="1">ROUND(IF($C48&gt;=userRetirementAge, IF($I48&gt;0, $I48*annualEffectivePostRetirementROI, 0), IF($I48&gt;0, $I48*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>49148421</v>
       </c>
       <c r="K48" s="6">
-        <f ca="1">ROUND(I48+J48, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>458718594</v>
       </c>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B49" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2064</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2065</v>
       </c>
       <c r="C49" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>97</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>74</v>
       </c>
       <c r="D49" s="5">
-        <f ca="1">ROUND(K48, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>458718594</v>
       </c>
       <c r="E49" s="14">
-        <f ca="1">ROUND(IF($C49&gt;userRetirementAge, IF($D49&gt;0,-FV(annualChangeInSWP, $C49-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E48+E48*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-5098826</v>
       </c>
       <c r="F49" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C49)</f>
@@ -3256,38 +3256,38 @@
         <v/>
       </c>
       <c r="H49" s="5">
-        <f ca="1">IF(AND($C49&gt;userRetirementAge, SUM($E49, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E49, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>471728.25</v>
       </c>
       <c r="I49" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>453148039.75</v>
       </c>
       <c r="J49" s="5">
-        <f ca="1">ROUND(IF($C49&gt;=userRetirementAge, IF($I49&gt;0, $I49*annualEffectivePostRetirementROI, 0), IF($I49&gt;0, $I49*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>54377765</v>
       </c>
       <c r="K49" s="6">
-        <f ca="1">ROUND(I49+J49, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>507525805</v>
       </c>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B50" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2065</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2066</v>
       </c>
       <c r="C50" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>98</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>75</v>
       </c>
       <c r="D50" s="5">
-        <f ca="1">ROUND(K49, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>507525805</v>
       </c>
       <c r="E50" s="14">
-        <f ca="1">ROUND(IF($C50&gt;userRetirementAge, IF($D50&gt;0,-FV(annualChangeInSWP, $C50-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E49+E49*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-5149815</v>
       </c>
       <c r="F50" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C50)</f>
@@ -3298,38 +3298,38 @@
         <v/>
       </c>
       <c r="H50" s="5">
-        <f ca="1">IF(AND($C50&gt;userRetirementAge, SUM($E50, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E50, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>478101.875</v>
       </c>
       <c r="I50" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>501897888.125</v>
       </c>
       <c r="J50" s="5">
-        <f ca="1">ROUND(IF($C50&gt;=userRetirementAge, IF($I50&gt;0, $I50*annualEffectivePostRetirementROI, 0), IF($I50&gt;0, $I50*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>60227747</v>
       </c>
       <c r="K50" s="6">
-        <f ca="1">ROUND(I50+J50, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>562125635</v>
       </c>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2066</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2067</v>
       </c>
       <c r="C51" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>99</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>76</v>
       </c>
       <c r="D51" s="5">
-        <f ca="1">ROUND(K50, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>562125635</v>
       </c>
       <c r="E51" s="14">
-        <f ca="1">ROUND(IF($C51&gt;userRetirementAge, IF($D51&gt;0,-FV(annualChangeInSWP, $C51-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E50+E50*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-5201313</v>
       </c>
       <c r="F51" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C51)</f>
@@ -3340,38 +3340,38 @@
         <v/>
       </c>
       <c r="H51" s="5">
-        <f ca="1">IF(AND($C51&gt;userRetirementAge, SUM($E51, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E51, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>484539.125</v>
       </c>
       <c r="I51" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>556439782.875</v>
       </c>
       <c r="J51" s="5">
-        <f ca="1">ROUND(IF($C51&gt;=userRetirementAge, IF($I51&gt;0, $I51*annualEffectivePostRetirementROI, 0), IF($I51&gt;0, $I51*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>66772774</v>
       </c>
       <c r="K51" s="6">
-        <f ca="1">ROUND(I51+J51, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>623212557</v>
       </c>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B52" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2067</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2068</v>
       </c>
       <c r="C52" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>100</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>77</v>
       </c>
       <c r="D52" s="5">
-        <f ca="1">ROUND(K51, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>623212557</v>
       </c>
       <c r="E52" s="14">
-        <f ca="1">ROUND(IF($C52&gt;userRetirementAge, IF($D52&gt;0,-FV(annualChangeInSWP, $C52-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E51+E51*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-5253326</v>
       </c>
       <c r="F52" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C52)</f>
@@ -3382,38 +3382,38 @@
         <v/>
       </c>
       <c r="H52" s="5">
-        <f ca="1">IF(AND($C52&gt;userRetirementAge, SUM($E52, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E52, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>491040.75</v>
       </c>
       <c r="I52" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>617468190.25</v>
       </c>
       <c r="J52" s="5">
-        <f ca="1">ROUND(IF($C52&gt;=userRetirementAge, IF($I52&gt;0, $I52*annualEffectivePostRetirementROI, 0), IF($I52&gt;0, $I52*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>74096183</v>
       </c>
       <c r="K52" s="6">
-        <f ca="1">ROUND(I52+J52, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>691564373</v>
       </c>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B53" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2068</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2069</v>
       </c>
       <c r="C53" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>101</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>78</v>
       </c>
       <c r="D53" s="5">
-        <f ca="1">ROUND(K52, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>691564373</v>
       </c>
       <c r="E53" s="14">
-        <f ca="1">ROUND(IF($C53&gt;userRetirementAge, IF($D53&gt;0,-FV(annualChangeInSWP, $C53-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E52+E52*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-5305859</v>
       </c>
       <c r="F53" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C53)</f>
@@ -3424,38 +3424,38 @@
         <v/>
       </c>
       <c r="H53" s="5">
-        <f ca="1">IF(AND($C53&gt;userRetirementAge, SUM($E53, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E53, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>497607.375</v>
       </c>
       <c r="I53" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>685760906.625</v>
       </c>
       <c r="J53" s="5">
-        <f ca="1">ROUND(IF($C53&gt;=userRetirementAge, IF($I53&gt;0, $I53*annualEffectivePostRetirementROI, 0), IF($I53&gt;0, $I53*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>82291309</v>
       </c>
       <c r="K53" s="6">
-        <f ca="1">ROUND(I53+J53, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>768052216</v>
       </c>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2069</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2070</v>
       </c>
       <c r="C54" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>102</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>79</v>
       </c>
       <c r="D54" s="5">
-        <f ca="1">ROUND(K53, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>768052216</v>
       </c>
       <c r="E54" s="14">
-        <f ca="1">ROUND(IF($C54&gt;userRetirementAge, IF($D54&gt;0,-FV(annualChangeInSWP, $C54-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E53+E53*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-5358918</v>
       </c>
       <c r="F54" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C54)</f>
@@ -3466,80 +3466,80 @@
         <v/>
       </c>
       <c r="H54" s="5">
-        <f ca="1">IF(AND($C54&gt;userRetirementAge, SUM($E54, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E54, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>504239.75</v>
       </c>
       <c r="I54" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>762189058.25</v>
       </c>
       <c r="J54" s="5">
-        <f ca="1">ROUND(IF($C54&gt;=userRetirementAge, IF($I54&gt;0, $I54*annualEffectivePostRetirementROI, 0), IF($I54&gt;0, $I54*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>91462687</v>
       </c>
       <c r="K54" s="6">
-        <f ca="1">ROUND(I54+J54, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>853651745</v>
       </c>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B55" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2070</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2071</v>
       </c>
       <c r="C55" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>103</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>80</v>
       </c>
       <c r="D55" s="5">
-        <f ca="1">ROUND(K54, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>853651745</v>
       </c>
       <c r="E55" s="14">
-        <f ca="1">ROUND(IF($C55&gt;userRetirementAge, IF($D55&gt;0,-FV(annualChangeInSWP, $C55-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E54+E54*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-5412507</v>
       </c>
       <c r="F55" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C55)</f>
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="G55" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="G55" ca="1">_xlfn.TEXTJOIN(", ", TRUE, IF('Input-Events'!E$4:E$106=$C55, 'Input-Events'!D$4:D$106, ""))</f>
-        <v/>
+        <v>Term Insurance, Life Expectancy</v>
       </c>
       <c r="H55" s="5">
-        <f ca="1">IF(AND($C55&gt;userRetirementAge, SUM($E55, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E55, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>510938.375</v>
       </c>
       <c r="I55" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>857728299.625</v>
       </c>
       <c r="J55" s="5">
-        <f ca="1">ROUND(IF($C55&gt;=userRetirementAge, IF($I55&gt;0, $I55*annualEffectivePostRetirementROI, 0), IF($I55&gt;0, $I55*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>102927396</v>
       </c>
       <c r="K55" s="6">
-        <f ca="1">ROUND(I55+J55, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>960655696</v>
       </c>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B56" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2071</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2072</v>
       </c>
       <c r="C56" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>104</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>81</v>
       </c>
       <c r="D56" s="5">
-        <f ca="1">ROUND(K55, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>960655696</v>
       </c>
       <c r="E56" s="14">
-        <f ca="1">ROUND(IF($C56&gt;userRetirementAge, IF($D56&gt;0,-FV(annualChangeInSWP, $C56-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E55+E55*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-5466632</v>
       </c>
       <c r="F56" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C56)</f>
@@ -3550,38 +3550,38 @@
         <v/>
       </c>
       <c r="H56" s="5">
-        <f ca="1">IF(AND($C56&gt;userRetirementAge, SUM($E56, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E56, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>517704</v>
       </c>
       <c r="I56" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>954671360</v>
       </c>
       <c r="J56" s="5">
-        <f ca="1">ROUND(IF($C56&gt;=userRetirementAge, IF($I56&gt;0, $I56*annualEffectivePostRetirementROI, 0), IF($I56&gt;0, $I56*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>114560563</v>
       </c>
       <c r="K56" s="6">
-        <f ca="1">ROUND(I56+J56, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>1069231923</v>
       </c>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B57" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2072</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2073</v>
       </c>
       <c r="C57" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>105</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>82</v>
       </c>
       <c r="D57" s="5">
-        <f ca="1">ROUND(K56, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>1069231923</v>
       </c>
       <c r="E57" s="14">
-        <f ca="1">ROUND(IF($C57&gt;userRetirementAge, IF($D57&gt;0,-FV(annualChangeInSWP, $C57-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E56+E56*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-5521298</v>
       </c>
       <c r="F57" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C57)</f>
@@ -3592,38 +3592,38 @@
         <v/>
       </c>
       <c r="H57" s="5">
-        <f ca="1">IF(AND($C57&gt;userRetirementAge, SUM($E57, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E57, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>524537.25</v>
       </c>
       <c r="I57" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>1063186087.75</v>
       </c>
       <c r="J57" s="5">
-        <f ca="1">ROUND(IF($C57&gt;=userRetirementAge, IF($I57&gt;0, $I57*annualEffectivePostRetirementROI, 0), IF($I57&gt;0, $I57*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>127582331</v>
       </c>
       <c r="K57" s="6">
-        <f ca="1">ROUND(I57+J57, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>1190768419</v>
       </c>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B58" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2073</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2074</v>
       </c>
       <c r="C58" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>106</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>83</v>
       </c>
       <c r="D58" s="5">
-        <f ca="1">ROUND(K57, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>1190768419</v>
       </c>
       <c r="E58" s="14">
-        <f ca="1">ROUND(IF($C58&gt;userRetirementAge, IF($D58&gt;0,-FV(annualChangeInSWP, $C58-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E57+E57*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-5576511</v>
       </c>
       <c r="F58" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C58)</f>
@@ -3634,38 +3634,38 @@
         <v/>
       </c>
       <c r="H58" s="5">
-        <f ca="1">IF(AND($C58&gt;userRetirementAge, SUM($E58, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E58, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>531438.875</v>
       </c>
       <c r="I58" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>1184660469.125</v>
       </c>
       <c r="J58" s="5">
-        <f ca="1">ROUND(IF($C58&gt;=userRetirementAge, IF($I58&gt;0, $I58*annualEffectivePostRetirementROI, 0), IF($I58&gt;0, $I58*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>142159256</v>
       </c>
       <c r="K58" s="6">
-        <f ca="1">ROUND(I58+J58, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>1326819725</v>
       </c>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B59" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2074</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2075</v>
       </c>
       <c r="C59" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>107</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>84</v>
       </c>
       <c r="D59" s="5">
-        <f ca="1">ROUND(K58, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>1326819725</v>
       </c>
       <c r="E59" s="14">
-        <f ca="1">ROUND(IF($C59&gt;userRetirementAge, IF($D59&gt;0,-FV(annualChangeInSWP, $C59-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E58+E58*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-5632276</v>
       </c>
       <c r="F59" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C59)</f>
@@ -3676,38 +3676,38 @@
         <v/>
       </c>
       <c r="H59" s="5">
-        <f ca="1">IF(AND($C59&gt;userRetirementAge, SUM($E59, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E59, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>538409.5</v>
       </c>
       <c r="I59" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>1320649039.5</v>
       </c>
       <c r="J59" s="5">
-        <f ca="1">ROUND(IF($C59&gt;=userRetirementAge, IF($I59&gt;0, $I59*annualEffectivePostRetirementROI, 0), IF($I59&gt;0, $I59*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>158477885</v>
       </c>
       <c r="K59" s="6">
-        <f ca="1">ROUND(I59+J59, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>1479126925</v>
       </c>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2075</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2076</v>
       </c>
       <c r="C60" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>108</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>85</v>
       </c>
       <c r="D60" s="5">
-        <f ca="1">ROUND(K59, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>1479126925</v>
       </c>
       <c r="E60" s="14">
-        <f ca="1">ROUND(IF($C60&gt;userRetirementAge, IF($D60&gt;0,-FV(annualChangeInSWP, $C60-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E59+E59*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-5688599</v>
       </c>
       <c r="F60" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C60)</f>
@@ -3718,38 +3718,38 @@
         <v/>
       </c>
       <c r="H60" s="5">
-        <f ca="1">IF(AND($C60&gt;userRetirementAge, SUM($E60, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E60, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>545449.875</v>
       </c>
       <c r="I60" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>1472892876.125</v>
       </c>
       <c r="J60" s="5">
-        <f ca="1">ROUND(IF($C60&gt;=userRetirementAge, IF($I60&gt;0, $I60*annualEffectivePostRetirementROI, 0), IF($I60&gt;0, $I60*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>176747145</v>
       </c>
       <c r="K60" s="6">
-        <f ca="1">ROUND(I60+J60, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>1649640021</v>
       </c>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2076</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2077</v>
       </c>
       <c r="C61" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>109</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>86</v>
       </c>
       <c r="D61" s="5">
-        <f ca="1">ROUND(K60, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>1649640021</v>
       </c>
       <c r="E61" s="14">
-        <f ca="1">ROUND(IF($C61&gt;userRetirementAge, IF($D61&gt;0,-FV(annualChangeInSWP, $C61-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E60+E60*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-5745485</v>
       </c>
       <c r="F61" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C61)</f>
@@ -3760,38 +3760,38 @@
         <v/>
       </c>
       <c r="H61" s="5">
-        <f ca="1">IF(AND($C61&gt;userRetirementAge, SUM($E61, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E61, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>552560.625</v>
       </c>
       <c r="I61" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>1643341975.375</v>
       </c>
       <c r="J61" s="5">
-        <f ca="1">ROUND(IF($C61&gt;=userRetirementAge, IF($I61&gt;0, $I61*annualEffectivePostRetirementROI, 0), IF($I61&gt;0, $I61*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>197201037</v>
       </c>
       <c r="K61" s="6">
-        <f ca="1">ROUND(I61+J61, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>1840543012</v>
       </c>
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B62" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2077</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2078</v>
       </c>
       <c r="C62" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>110</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>87</v>
       </c>
       <c r="D62" s="5">
-        <f ca="1">ROUND(K61, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>1840543012</v>
       </c>
       <c r="E62" s="14">
-        <f ca="1">ROUND(IF($C62&gt;userRetirementAge, IF($D62&gt;0,-FV(annualChangeInSWP, $C62-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E61+E61*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-5802940</v>
       </c>
       <c r="F62" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C62)</f>
@@ -3802,38 +3802,38 @@
         <v/>
       </c>
       <c r="H62" s="5">
-        <f ca="1">IF(AND($C62&gt;userRetirementAge, SUM($E62, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E62, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>559742.5</v>
       </c>
       <c r="I62" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>1834180329.5</v>
       </c>
       <c r="J62" s="5">
-        <f ca="1">ROUND(IF($C62&gt;=userRetirementAge, IF($I62&gt;0, $I62*annualEffectivePostRetirementROI, 0), IF($I62&gt;0, $I62*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>220101640</v>
       </c>
       <c r="K62" s="6">
-        <f ca="1">ROUND(I62+J62, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>2054281970</v>
       </c>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B63" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2078</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2079</v>
       </c>
       <c r="C63" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>111</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>88</v>
       </c>
       <c r="D63" s="5">
-        <f ca="1">ROUND(K62, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>2054281970</v>
       </c>
       <c r="E63" s="14">
-        <f ca="1">ROUND(IF($C63&gt;userRetirementAge, IF($D63&gt;0,-FV(annualChangeInSWP, $C63-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E62+E62*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-5860969</v>
       </c>
       <c r="F63" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C63)</f>
@@ -3844,38 +3844,38 @@
         <v/>
       </c>
       <c r="H63" s="5">
-        <f ca="1">IF(AND($C63&gt;userRetirementAge, SUM($E63, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E63, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>566996.125</v>
       </c>
       <c r="I63" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>2047854004.875</v>
       </c>
       <c r="J63" s="5">
-        <f ca="1">ROUND(IF($C63&gt;=userRetirementAge, IF($I63&gt;0, $I63*annualEffectivePostRetirementROI, 0), IF($I63&gt;0, $I63*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>245742481</v>
       </c>
       <c r="K63" s="6">
-        <f ca="1">ROUND(I63+J63, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>2293596486</v>
       </c>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B64" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2079</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2080</v>
       </c>
       <c r="C64" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>112</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>89</v>
       </c>
       <c r="D64" s="5">
-        <f ca="1">ROUND(K63, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>2293596486</v>
       </c>
       <c r="E64" s="14">
-        <f ca="1">ROUND(IF($C64&gt;userRetirementAge, IF($D64&gt;0,-FV(annualChangeInSWP, $C64-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E63+E63*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-5919579</v>
       </c>
       <c r="F64" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C64)</f>
@@ -3886,38 +3886,38 @@
         <v/>
       </c>
       <c r="H64" s="5">
-        <f ca="1">IF(AND($C64&gt;userRetirementAge, SUM($E64, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E64, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>574322.375</v>
       </c>
       <c r="I64" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>2287102584.625</v>
       </c>
       <c r="J64" s="5">
-        <f ca="1">ROUND(IF($C64&gt;=userRetirementAge, IF($I64&gt;0, $I64*annualEffectivePostRetirementROI, 0), IF($I64&gt;0, $I64*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>274452310</v>
       </c>
       <c r="K64" s="6">
-        <f ca="1">ROUND(I64+J64, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>2561554895</v>
       </c>
     </row>
     <row r="65" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B65" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2080</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2081</v>
       </c>
       <c r="C65" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>113</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>90</v>
       </c>
       <c r="D65" s="5">
-        <f ca="1">ROUND(K64, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>2561554895</v>
       </c>
       <c r="E65" s="14">
-        <f ca="1">ROUND(IF($C65&gt;userRetirementAge, IF($D65&gt;0,-FV(annualChangeInSWP, $C65-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E64+E64*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-5978775</v>
       </c>
       <c r="F65" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C65)</f>
@@ -3928,38 +3928,38 @@
         <v/>
       </c>
       <c r="H65" s="5">
-        <f ca="1">IF(AND($C65&gt;userRetirementAge, SUM($E65, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E65, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>581721.875</v>
       </c>
       <c r="I65" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>2554994398.125</v>
       </c>
       <c r="J65" s="5">
-        <f ca="1">ROUND(IF($C65&gt;=userRetirementAge, IF($I65&gt;0, $I65*annualEffectivePostRetirementROI, 0), IF($I65&gt;0, $I65*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>306599328</v>
       </c>
       <c r="K65" s="6">
-        <f ca="1">ROUND(I65+J65, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>2861593726</v>
       </c>
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B66" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2081</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2082</v>
       </c>
       <c r="C66" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>114</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>91</v>
       </c>
       <c r="D66" s="5">
-        <f ca="1">ROUND(K65, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>2861593726</v>
       </c>
       <c r="E66" s="14">
-        <f ca="1">ROUND(IF($C66&gt;userRetirementAge, IF($D66&gt;0,-FV(annualChangeInSWP, $C66-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E65+E65*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-6038563</v>
       </c>
       <c r="F66" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C66)</f>
@@ -3970,38 +3970,38 @@
         <v/>
       </c>
       <c r="H66" s="5">
-        <f ca="1">IF(AND($C66&gt;userRetirementAge, SUM($E66, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E66, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>589195.375</v>
       </c>
       <c r="I66" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>2854965967.625</v>
       </c>
       <c r="J66" s="5">
-        <f ca="1">ROUND(IF($C66&gt;=userRetirementAge, IF($I66&gt;0, $I66*annualEffectivePostRetirementROI, 0), IF($I66&gt;0, $I66*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>342595916</v>
       </c>
       <c r="K66" s="6">
-        <f ca="1">ROUND(I66+J66, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>3197561884</v>
       </c>
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B67" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2082</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2083</v>
       </c>
       <c r="C67" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>115</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>92</v>
       </c>
       <c r="D67" s="5">
-        <f ca="1">ROUND(K66, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>3197561884</v>
       </c>
       <c r="E67" s="14">
-        <f ca="1">ROUND(IF($C67&gt;userRetirementAge, IF($D67&gt;0,-FV(annualChangeInSWP, $C67-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E66+E66*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-6098948</v>
       </c>
       <c r="F67" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C67)</f>
@@ -4012,38 +4012,38 @@
         <v/>
       </c>
       <c r="H67" s="5">
-        <f ca="1">IF(AND($C67&gt;userRetirementAge, SUM($E67, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E67, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>596743.5</v>
       </c>
       <c r="I67" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>3190866192.5</v>
       </c>
       <c r="J67" s="5">
-        <f ca="1">ROUND(IF($C67&gt;=userRetirementAge, IF($I67&gt;0, $I67*annualEffectivePostRetirementROI, 0), IF($I67&gt;0, $I67*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>382903943</v>
       </c>
       <c r="K67" s="6">
-        <f ca="1">ROUND(I67+J67, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>3573770136</v>
       </c>
     </row>
     <row r="68" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B68" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2083</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2084</v>
       </c>
       <c r="C68" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>116</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>93</v>
       </c>
       <c r="D68" s="5">
-        <f ca="1">ROUND(K67, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>3573770136</v>
       </c>
       <c r="E68" s="14">
-        <f ca="1">ROUND(IF($C68&gt;userRetirementAge, IF($D68&gt;0,-FV(annualChangeInSWP, $C68-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E67+E67*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-6159938</v>
       </c>
       <c r="F68" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C68)</f>
@@ -4054,38 +4054,38 @@
         <v/>
       </c>
       <c r="H68" s="5">
-        <f ca="1">IF(AND($C68&gt;userRetirementAge, SUM($E68, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E68, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>604367.25</v>
       </c>
       <c r="I68" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>3567005830.75</v>
       </c>
       <c r="J68" s="5">
-        <f ca="1">ROUND(IF($C68&gt;=userRetirementAge, IF($I68&gt;0, $I68*annualEffectivePostRetirementROI, 0), IF($I68&gt;0, $I68*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>428040700</v>
       </c>
       <c r="K68" s="6">
-        <f ca="1">ROUND(I68+J68, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>3995046531</v>
       </c>
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B69" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2084</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2085</v>
       </c>
       <c r="C69" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>117</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>94</v>
       </c>
       <c r="D69" s="5">
-        <f ca="1">ROUND(K68, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>3995046531</v>
       </c>
       <c r="E69" s="14">
-        <f ca="1">ROUND(IF($C69&gt;userRetirementAge, IF($D69&gt;0,-FV(annualChangeInSWP, $C69-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E68+E68*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-6221537</v>
       </c>
       <c r="F69" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C69)</f>
@@ -4096,38 +4096,38 @@
         <v/>
       </c>
       <c r="H69" s="5">
-        <f ca="1">IF(AND($C69&gt;userRetirementAge, SUM($E69, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E69, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>612067.125</v>
       </c>
       <c r="I69" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>3988212926.875</v>
       </c>
       <c r="J69" s="5">
-        <f ca="1">ROUND(IF($C69&gt;=userRetirementAge, IF($I69&gt;0, $I69*annualEffectivePostRetirementROI, 0), IF($I69&gt;0, $I69*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>478585551</v>
       </c>
       <c r="K69" s="6">
-        <f ca="1">ROUND(I69+J69, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>4466798478</v>
       </c>
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B70" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2085</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2086</v>
       </c>
       <c r="C70" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>118</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>95</v>
       </c>
       <c r="D70" s="5">
-        <f ca="1">ROUND(K69, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>4466798478</v>
       </c>
       <c r="E70" s="14">
-        <f ca="1">ROUND(IF($C70&gt;userRetirementAge, IF($D70&gt;0,-FV(annualChangeInSWP, $C70-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E69+E69*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-6283752</v>
       </c>
       <c r="F70" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C70)</f>
@@ -4138,38 +4138,38 @@
         <v/>
       </c>
       <c r="H70" s="5">
-        <f ca="1">IF(AND($C70&gt;userRetirementAge, SUM($E70, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E70, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>619844</v>
       </c>
       <c r="I70" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>4459894882</v>
       </c>
       <c r="J70" s="5">
-        <f ca="1">ROUND(IF($C70&gt;=userRetirementAge, IF($I70&gt;0, $I70*annualEffectivePostRetirementROI, 0), IF($I70&gt;0, $I70*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>535187386</v>
       </c>
       <c r="K70" s="6">
-        <f ca="1">ROUND(I70+J70, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>4995082268</v>
       </c>
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B71" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2086</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2087</v>
       </c>
       <c r="C71" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>119</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>96</v>
       </c>
       <c r="D71" s="5">
-        <f ca="1">ROUND(K70, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>4995082268</v>
       </c>
       <c r="E71" s="14">
-        <f ca="1">ROUND(IF($C71&gt;userRetirementAge, IF($D71&gt;0,-FV(annualChangeInSWP, $C71-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E70+E70*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-6346590</v>
       </c>
       <c r="F71" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C71)</f>
@@ -4180,38 +4180,38 @@
         <v/>
       </c>
       <c r="H71" s="5">
-        <f ca="1">IF(AND($C71&gt;userRetirementAge, SUM($E71, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E71, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>627698.75</v>
       </c>
       <c r="I71" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>4988107979.25</v>
       </c>
       <c r="J71" s="5">
-        <f ca="1">ROUND(IF($C71&gt;=userRetirementAge, IF($I71&gt;0, $I71*annualEffectivePostRetirementROI, 0), IF($I71&gt;0, $I71*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>598572958</v>
       </c>
       <c r="K71" s="6">
-        <f ca="1">ROUND(I71+J71, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>5586680937</v>
       </c>
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B72" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2087</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2088</v>
       </c>
       <c r="C72" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>120</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>97</v>
       </c>
       <c r="D72" s="5">
-        <f ca="1">ROUND(K71, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>5586680937</v>
       </c>
       <c r="E72" s="14">
-        <f ca="1">ROUND(IF($C72&gt;userRetirementAge, IF($D72&gt;0,-FV(annualChangeInSWP, $C72-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E71+E71*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-6410056</v>
       </c>
       <c r="F72" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C72)</f>
@@ -4222,38 +4222,38 @@
         <v/>
       </c>
       <c r="H72" s="5">
-        <f ca="1">IF(AND($C72&gt;userRetirementAge, SUM($E72, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E72, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>635632</v>
       </c>
       <c r="I72" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>5579635249</v>
       </c>
       <c r="J72" s="5">
-        <f ca="1">ROUND(IF($C72&gt;=userRetirementAge, IF($I72&gt;0, $I72*annualEffectivePostRetirementROI, 0), IF($I72&gt;0, $I72*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>669556230</v>
       </c>
       <c r="K72" s="6">
-        <f ca="1">ROUND(I72+J72, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>6249191479</v>
       </c>
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B73" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2088</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2089</v>
       </c>
       <c r="C73" s="4">
-        <f t="shared" ca="1" si="4"/>
-        <v>121</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>98</v>
       </c>
       <c r="D73" s="5">
-        <f ca="1">ROUND(K72, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>6249191479</v>
       </c>
       <c r="E73" s="14">
-        <f ca="1">ROUND(IF($C73&gt;userRetirementAge, IF($D73&gt;0,-FV(annualChangeInSWP, $C73-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E72+E72*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-6474156</v>
       </c>
       <c r="F73" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C73)</f>
@@ -4264,38 +4264,38 @@
         <v/>
       </c>
       <c r="H73" s="5">
-        <f ca="1">IF(AND($C73&gt;userRetirementAge, SUM($E73, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E73, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ref="H73:H109" ca="1" si="15">IF(AND($C73&gt;userRetirementAge, SUM($E73, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E73, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
+        <v>643644.5</v>
       </c>
       <c r="I73" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>6242073678.5</v>
       </c>
       <c r="J73" s="5">
-        <f ca="1">ROUND(IF($C73&gt;=userRetirementAge, IF($I73&gt;0, $I73*annualEffectivePostRetirementROI, 0), IF($I73&gt;0, $I73*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ref="J73:J109" ca="1" si="16">ROUND(IF($C73&gt;=userRetirementAge, IF($I73&gt;0, $I73*annualEffectivePostRetirementROI, 0), IF($I73&gt;0, $I73*annualEffectiveROI, 0)), 0)</f>
+        <v>749048841</v>
       </c>
       <c r="K73" s="6">
-        <f ca="1">ROUND(I73+J73, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ref="K73:K104" ca="1" si="17">ROUND(I73+J73, 0)</f>
+        <v>6991122520</v>
       </c>
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" s="3">
-        <f t="shared" ref="B74:B109" ca="1" si="5">B73+1</f>
-        <v>2089</v>
+        <f t="shared" ref="B74:B109" ca="1" si="18">B73+1</f>
+        <v>2090</v>
       </c>
       <c r="C74" s="4">
-        <f t="shared" ref="C74:C109" ca="1" si="6">C73+1</f>
-        <v>122</v>
+        <f t="shared" ref="C74:C109" ca="1" si="19">C73+1</f>
+        <v>99</v>
       </c>
       <c r="D74" s="5">
-        <f ca="1">ROUND(K73, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ref="D74:D109" ca="1" si="20">ROUND(K73, 0)</f>
+        <v>6991122520</v>
       </c>
       <c r="E74" s="14">
-        <f ca="1">ROUND(IF($C74&gt;userRetirementAge, IF($D74&gt;0,-FV(annualChangeInSWP, $C74-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E73+E73*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ref="E74:E109" ca="1" si="21">ROUND(IF($C74&gt;userRetirementAge, IF($D74&gt;0,-FV(annualChangeInSWP, $C74-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E73+E73*(annualIncreaseInSavings)), 0)</f>
+        <v>-6538898</v>
       </c>
       <c r="F74" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C74)</f>
@@ -4306,38 +4306,38 @@
         <v/>
       </c>
       <c r="H74" s="5">
-        <f ca="1">IF(AND($C74&gt;userRetirementAge, SUM($E74, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E74, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>651737.25</v>
       </c>
       <c r="I74" s="5">
-        <f t="shared" ref="I74:I109" ca="1" si="7">$D74+$E74+$F74-$H74</f>
-        <v>-1546418</v>
+        <f t="shared" ref="I74:I109" ca="1" si="22">$D74+$E74+$F74-$H74</f>
+        <v>6983931884.75</v>
       </c>
       <c r="J74" s="5">
-        <f ca="1">ROUND(IF($C74&gt;=userRetirementAge, IF($I74&gt;0, $I74*annualEffectivePostRetirementROI, 0), IF($I74&gt;0, $I74*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>838071826</v>
       </c>
       <c r="K74" s="6">
-        <f ca="1">ROUND(I74+J74, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>7822003711</v>
       </c>
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B75" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2090</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2091</v>
       </c>
       <c r="C75" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>123</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>100</v>
       </c>
       <c r="D75" s="5">
-        <f ca="1">ROUND(K74, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>7822003711</v>
       </c>
       <c r="E75" s="14">
-        <f ca="1">ROUND(IF($C75&gt;userRetirementAge, IF($D75&gt;0,-FV(annualChangeInSWP, $C75-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E74+E74*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-6604287</v>
       </c>
       <c r="F75" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C75)</f>
@@ -4348,38 +4348,38 @@
         <v/>
       </c>
       <c r="H75" s="5">
-        <f ca="1">IF(AND($C75&gt;userRetirementAge, SUM($E75, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E75, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>659910.875</v>
       </c>
       <c r="I75" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>7814739513.125</v>
       </c>
       <c r="J75" s="5">
-        <f ca="1">ROUND(IF($C75&gt;=userRetirementAge, IF($I75&gt;0, $I75*annualEffectivePostRetirementROI, 0), IF($I75&gt;0, $I75*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>937768742</v>
       </c>
       <c r="K75" s="6">
-        <f ca="1">ROUND(I75+J75, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>8752508255</v>
       </c>
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B76" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2091</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2092</v>
       </c>
       <c r="C76" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>124</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>101</v>
       </c>
       <c r="D76" s="5">
-        <f ca="1">ROUND(K75, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>8752508255</v>
       </c>
       <c r="E76" s="14">
-        <f ca="1">ROUND(IF($C76&gt;userRetirementAge, IF($D76&gt;0,-FV(annualChangeInSWP, $C76-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E75+E75*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-6670330</v>
       </c>
       <c r="F76" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C76)</f>
@@ -4390,38 +4390,38 @@
         <v/>
       </c>
       <c r="H76" s="5">
-        <f ca="1">IF(AND($C76&gt;userRetirementAge, SUM($E76, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E76, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>668166.25</v>
       </c>
       <c r="I76" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>8745169758.75</v>
       </c>
       <c r="J76" s="5">
-        <f ca="1">ROUND(IF($C76&gt;=userRetirementAge, IF($I76&gt;0, $I76*annualEffectivePostRetirementROI, 0), IF($I76&gt;0, $I76*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>1049420371</v>
       </c>
       <c r="K76" s="6">
-        <f ca="1">ROUND(I76+J76, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>9794590130</v>
       </c>
     </row>
     <row r="77" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B77" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2092</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2093</v>
       </c>
       <c r="C77" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>125</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>102</v>
       </c>
       <c r="D77" s="5">
-        <f ca="1">ROUND(K76, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>9794590130</v>
       </c>
       <c r="E77" s="14">
-        <f ca="1">ROUND(IF($C77&gt;userRetirementAge, IF($D77&gt;0,-FV(annualChangeInSWP, $C77-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E76+E76*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-6737033</v>
       </c>
       <c r="F77" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C77)</f>
@@ -4432,38 +4432,38 @@
         <v/>
       </c>
       <c r="H77" s="5">
-        <f ca="1">IF(AND($C77&gt;userRetirementAge, SUM($E77, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E77, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>676504.125</v>
       </c>
       <c r="I77" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>9787176592.875</v>
       </c>
       <c r="J77" s="5">
-        <f ca="1">ROUND(IF($C77&gt;=userRetirementAge, IF($I77&gt;0, $I77*annualEffectivePostRetirementROI, 0), IF($I77&gt;0, $I77*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>1174461191</v>
       </c>
       <c r="K77" s="6">
-        <f ca="1">ROUND(I77+J77, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>10961637784</v>
       </c>
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B78" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2093</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2094</v>
       </c>
       <c r="C78" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>126</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>103</v>
       </c>
       <c r="D78" s="5">
-        <f ca="1">ROUND(K77, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>10961637784</v>
       </c>
       <c r="E78" s="14">
-        <f ca="1">ROUND(IF($C78&gt;userRetirementAge, IF($D78&gt;0,-FV(annualChangeInSWP, $C78-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E77+E77*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-6804404</v>
       </c>
       <c r="F78" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C78)</f>
@@ -4474,38 +4474,38 @@
         <v/>
       </c>
       <c r="H78" s="5">
-        <f ca="1">IF(AND($C78&gt;userRetirementAge, SUM($E78, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E78, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>684925.5</v>
       </c>
       <c r="I78" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>10954148454.5</v>
       </c>
       <c r="J78" s="5">
-        <f ca="1">ROUND(IF($C78&gt;=userRetirementAge, IF($I78&gt;0, $I78*annualEffectivePostRetirementROI, 0), IF($I78&gt;0, $I78*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>1314497815</v>
       </c>
       <c r="K78" s="6">
-        <f ca="1">ROUND(I78+J78, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>12268646270</v>
       </c>
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B79" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2094</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2095</v>
       </c>
       <c r="C79" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>127</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>104</v>
       </c>
       <c r="D79" s="5">
-        <f ca="1">ROUND(K78, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>12268646270</v>
       </c>
       <c r="E79" s="14">
-        <f ca="1">ROUND(IF($C79&gt;userRetirementAge, IF($D79&gt;0,-FV(annualChangeInSWP, $C79-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E78+E78*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-6872448</v>
       </c>
       <c r="F79" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C79)</f>
@@ -4516,38 +4516,38 @@
         <v/>
       </c>
       <c r="H79" s="5">
-        <f ca="1">IF(AND($C79&gt;userRetirementAge, SUM($E79, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E79, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>693431</v>
       </c>
       <c r="I79" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>12261080391</v>
       </c>
       <c r="J79" s="5">
-        <f ca="1">ROUND(IF($C79&gt;=userRetirementAge, IF($I79&gt;0, $I79*annualEffectivePostRetirementROI, 0), IF($I79&gt;0, $I79*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>1471329647</v>
       </c>
       <c r="K79" s="6">
-        <f ca="1">ROUND(I79+J79, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>13732410038</v>
       </c>
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B80" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2095</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2096</v>
       </c>
       <c r="C80" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>128</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>105</v>
       </c>
       <c r="D80" s="5">
-        <f ca="1">ROUND(K79, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>13732410038</v>
       </c>
       <c r="E80" s="14">
-        <f ca="1">ROUND(IF($C80&gt;userRetirementAge, IF($D80&gt;0,-FV(annualChangeInSWP, $C80-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E79+E79*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-6941172</v>
       </c>
       <c r="F80" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C80)</f>
@@ -4558,38 +4558,38 @@
         <v/>
       </c>
       <c r="H80" s="5">
-        <f ca="1">IF(AND($C80&gt;userRetirementAge, SUM($E80, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E80, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>702021.5</v>
       </c>
       <c r="I80" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>13724766844.5</v>
       </c>
       <c r="J80" s="5">
-        <f ca="1">ROUND(IF($C80&gt;=userRetirementAge, IF($I80&gt;0, $I80*annualEffectivePostRetirementROI, 0), IF($I80&gt;0, $I80*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>1646972021</v>
       </c>
       <c r="K80" s="6">
-        <f ca="1">ROUND(I80+J80, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>15371738866</v>
       </c>
     </row>
     <row r="81" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B81" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2096</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2097</v>
       </c>
       <c r="C81" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>129</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>106</v>
       </c>
       <c r="D81" s="5">
-        <f ca="1">ROUND(K80, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>15371738866</v>
       </c>
       <c r="E81" s="14">
-        <f ca="1">ROUND(IF($C81&gt;userRetirementAge, IF($D81&gt;0,-FV(annualChangeInSWP, $C81-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E80+E80*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-7010584</v>
       </c>
       <c r="F81" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C81)</f>
@@ -4600,38 +4600,38 @@
         <v/>
       </c>
       <c r="H81" s="5">
-        <f ca="1">IF(AND($C81&gt;userRetirementAge, SUM($E81, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E81, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>710698</v>
       </c>
       <c r="I81" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>15364017584</v>
       </c>
       <c r="J81" s="5">
-        <f ca="1">ROUND(IF($C81&gt;=userRetirementAge, IF($I81&gt;0, $I81*annualEffectivePostRetirementROI, 0), IF($I81&gt;0, $I81*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>1843682110</v>
       </c>
       <c r="K81" s="6">
-        <f ca="1">ROUND(I81+J81, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>17207699694</v>
       </c>
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2097</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2098</v>
       </c>
       <c r="C82" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>130</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>107</v>
       </c>
       <c r="D82" s="5">
-        <f ca="1">ROUND(K81, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>17207699694</v>
       </c>
       <c r="E82" s="14">
-        <f ca="1">ROUND(IF($C82&gt;userRetirementAge, IF($D82&gt;0,-FV(annualChangeInSWP, $C82-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E81+E81*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-7080690</v>
       </c>
       <c r="F82" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C82)</f>
@@ -4642,38 +4642,38 @@
         <v/>
       </c>
       <c r="H82" s="5">
-        <f ca="1">IF(AND($C82&gt;userRetirementAge, SUM($E82, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E82, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>719461.25</v>
       </c>
       <c r="I82" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>17199899542.75</v>
       </c>
       <c r="J82" s="5">
-        <f ca="1">ROUND(IF($C82&gt;=userRetirementAge, IF($I82&gt;0, $I82*annualEffectivePostRetirementROI, 0), IF($I82&gt;0, $I82*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>2063987945</v>
       </c>
       <c r="K82" s="6">
-        <f ca="1">ROUND(I82+J82, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>19263887488</v>
       </c>
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B83" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2098</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2099</v>
       </c>
       <c r="C83" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>131</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>108</v>
       </c>
       <c r="D83" s="5">
-        <f ca="1">ROUND(K82, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>19263887488</v>
       </c>
       <c r="E83" s="14">
-        <f ca="1">ROUND(IF($C83&gt;userRetirementAge, IF($D83&gt;0,-FV(annualChangeInSWP, $C83-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E82+E82*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-7151496</v>
       </c>
       <c r="F83" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C83)</f>
@@ -4684,38 +4684,38 @@
         <v/>
       </c>
       <c r="H83" s="5">
-        <f ca="1">IF(AND($C83&gt;userRetirementAge, SUM($E83, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E83, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>728312</v>
       </c>
       <c r="I83" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>19256007680</v>
       </c>
       <c r="J83" s="5">
-        <f ca="1">ROUND(IF($C83&gt;=userRetirementAge, IF($I83&gt;0, $I83*annualEffectivePostRetirementROI, 0), IF($I83&gt;0, $I83*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>2310720922</v>
       </c>
       <c r="K83" s="6">
-        <f ca="1">ROUND(I83+J83, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>21566728602</v>
       </c>
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B84" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2099</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2100</v>
       </c>
       <c r="C84" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>132</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>109</v>
       </c>
       <c r="D84" s="5">
-        <f ca="1">ROUND(K83, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>21566728602</v>
       </c>
       <c r="E84" s="14">
-        <f ca="1">ROUND(IF($C84&gt;userRetirementAge, IF($D84&gt;0,-FV(annualChangeInSWP, $C84-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E83+E83*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-7223011</v>
       </c>
       <c r="F84" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C84)</f>
@@ -4726,38 +4726,38 @@
         <v/>
       </c>
       <c r="H84" s="5">
-        <f ca="1">IF(AND($C84&gt;userRetirementAge, SUM($E84, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E84, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>737251.375</v>
       </c>
       <c r="I84" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>21558768339.625</v>
       </c>
       <c r="J84" s="5">
-        <f ca="1">ROUND(IF($C84&gt;=userRetirementAge, IF($I84&gt;0, $I84*annualEffectivePostRetirementROI, 0), IF($I84&gt;0, $I84*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>2587052201</v>
       </c>
       <c r="K84" s="6">
-        <f ca="1">ROUND(I84+J84, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>24145820541</v>
       </c>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B85" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2100</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2101</v>
       </c>
       <c r="C85" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>133</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>110</v>
       </c>
       <c r="D85" s="5">
-        <f ca="1">ROUND(K84, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>24145820541</v>
       </c>
       <c r="E85" s="14">
-        <f ca="1">ROUND(IF($C85&gt;userRetirementAge, IF($D85&gt;0,-FV(annualChangeInSWP, $C85-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E84+E84*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-7295242</v>
       </c>
       <c r="F85" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C85)</f>
@@ -4768,38 +4768,38 @@
         <v/>
       </c>
       <c r="H85" s="5">
-        <f ca="1">IF(AND($C85&gt;userRetirementAge, SUM($E85, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E85, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>746280.25</v>
       </c>
       <c r="I85" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>24137779018.75</v>
       </c>
       <c r="J85" s="5">
-        <f ca="1">ROUND(IF($C85&gt;=userRetirementAge, IF($I85&gt;0, $I85*annualEffectivePostRetirementROI, 0), IF($I85&gt;0, $I85*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>2896533482</v>
       </c>
       <c r="K85" s="6">
-        <f ca="1">ROUND(I85+J85, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>27034312501</v>
       </c>
     </row>
     <row r="86" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B86" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2101</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2102</v>
       </c>
       <c r="C86" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>134</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>111</v>
       </c>
       <c r="D86" s="5">
-        <f ca="1">ROUND(K85, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>27034312501</v>
       </c>
       <c r="E86" s="14">
-        <f ca="1">ROUND(IF($C86&gt;userRetirementAge, IF($D86&gt;0,-FV(annualChangeInSWP, $C86-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E85+E85*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-7368194</v>
       </c>
       <c r="F86" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C86)</f>
@@ -4810,38 +4810,38 @@
         <v/>
       </c>
       <c r="H86" s="5">
-        <f ca="1">IF(AND($C86&gt;userRetirementAge, SUM($E86, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E86, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>755399.25</v>
       </c>
       <c r="I86" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>27026188907.75</v>
       </c>
       <c r="J86" s="5">
-        <f ca="1">ROUND(IF($C86&gt;=userRetirementAge, IF($I86&gt;0, $I86*annualEffectivePostRetirementROI, 0), IF($I86&gt;0, $I86*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>3243142669</v>
       </c>
       <c r="K86" s="6">
-        <f ca="1">ROUND(I86+J86, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>30269331577</v>
       </c>
     </row>
     <row r="87" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B87" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2102</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2103</v>
       </c>
       <c r="C87" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>135</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>112</v>
       </c>
       <c r="D87" s="5">
-        <f ca="1">ROUND(K86, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>30269331577</v>
       </c>
       <c r="E87" s="14">
-        <f ca="1">ROUND(IF($C87&gt;userRetirementAge, IF($D87&gt;0,-FV(annualChangeInSWP, $C87-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E86+E86*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-7441876</v>
       </c>
       <c r="F87" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C87)</f>
@@ -4852,38 +4852,38 @@
         <v/>
       </c>
       <c r="H87" s="5">
-        <f ca="1">IF(AND($C87&gt;userRetirementAge, SUM($E87, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E87, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>764609.5</v>
       </c>
       <c r="I87" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>30261125091.5</v>
       </c>
       <c r="J87" s="5">
-        <f ca="1">ROUND(IF($C87&gt;=userRetirementAge, IF($I87&gt;0, $I87*annualEffectivePostRetirementROI, 0), IF($I87&gt;0, $I87*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>3631335011</v>
       </c>
       <c r="K87" s="6">
-        <f ca="1">ROUND(I87+J87, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>33892460103</v>
       </c>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B88" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2103</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2104</v>
       </c>
       <c r="C88" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>136</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>113</v>
       </c>
       <c r="D88" s="5">
-        <f ca="1">ROUND(K87, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>33892460103</v>
       </c>
       <c r="E88" s="14">
-        <f ca="1">ROUND(IF($C88&gt;userRetirementAge, IF($D88&gt;0,-FV(annualChangeInSWP, $C88-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E87+E87*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-7516295</v>
       </c>
       <c r="F88" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C88)</f>
@@ -4894,38 +4894,38 @@
         <v/>
       </c>
       <c r="H88" s="5">
-        <f ca="1">IF(AND($C88&gt;userRetirementAge, SUM($E88, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E88, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>773911.875</v>
       </c>
       <c r="I88" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>33884169896.125</v>
       </c>
       <c r="J88" s="5">
-        <f ca="1">ROUND(IF($C88&gt;=userRetirementAge, IF($I88&gt;0, $I88*annualEffectivePostRetirementROI, 0), IF($I88&gt;0, $I88*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>4066100388</v>
       </c>
       <c r="K88" s="6">
-        <f ca="1">ROUND(I88+J88, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>37950270284</v>
       </c>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B89" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2104</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2105</v>
       </c>
       <c r="C89" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>137</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>114</v>
       </c>
       <c r="D89" s="5">
-        <f ca="1">ROUND(K88, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>37950270284</v>
       </c>
       <c r="E89" s="14">
-        <f ca="1">ROUND(IF($C89&gt;userRetirementAge, IF($D89&gt;0,-FV(annualChangeInSWP, $C89-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E88+E88*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-7591458</v>
       </c>
       <c r="F89" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C89)</f>
@@ -4936,38 +4936,38 @@
         <v/>
       </c>
       <c r="H89" s="5">
-        <f ca="1">IF(AND($C89&gt;userRetirementAge, SUM($E89, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E89, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>783307.25</v>
       </c>
       <c r="I89" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>37941895518.75</v>
       </c>
       <c r="J89" s="5">
-        <f ca="1">ROUND(IF($C89&gt;=userRetirementAge, IF($I89&gt;0, $I89*annualEffectivePostRetirementROI, 0), IF($I89&gt;0, $I89*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>4553027462</v>
       </c>
       <c r="K89" s="6">
-        <f ca="1">ROUND(I89+J89, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>42494922981</v>
       </c>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B90" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2105</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2106</v>
       </c>
       <c r="C90" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>138</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>115</v>
       </c>
       <c r="D90" s="5">
-        <f ca="1">ROUND(K89, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>42494922981</v>
       </c>
       <c r="E90" s="14">
-        <f ca="1">ROUND(IF($C90&gt;userRetirementAge, IF($D90&gt;0,-FV(annualChangeInSWP, $C90-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E89+E89*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-7667372</v>
       </c>
       <c r="F90" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C90)</f>
@@ -4978,38 +4978,38 @@
         <v/>
       </c>
       <c r="H90" s="5">
-        <f ca="1">IF(AND($C90&gt;userRetirementAge, SUM($E90, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E90, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>792796.5</v>
       </c>
       <c r="I90" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>42486462812.5</v>
       </c>
       <c r="J90" s="5">
-        <f ca="1">ROUND(IF($C90&gt;=userRetirementAge, IF($I90&gt;0, $I90*annualEffectivePostRetirementROI, 0), IF($I90&gt;0, $I90*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>5098375538</v>
       </c>
       <c r="K90" s="6">
-        <f ca="1">ROUND(I90+J90, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>47584838351</v>
       </c>
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B91" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2106</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2107</v>
       </c>
       <c r="C91" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>139</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>116</v>
       </c>
       <c r="D91" s="5">
-        <f ca="1">ROUND(K90, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>47584838351</v>
       </c>
       <c r="E91" s="14">
-        <f ca="1">ROUND(IF($C91&gt;userRetirementAge, IF($D91&gt;0,-FV(annualChangeInSWP, $C91-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E90+E90*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-7744046</v>
       </c>
       <c r="F91" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C91)</f>
@@ -5020,38 +5020,38 @@
         <v/>
       </c>
       <c r="H91" s="5">
-        <f ca="1">IF(AND($C91&gt;userRetirementAge, SUM($E91, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E91, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>802380.75</v>
       </c>
       <c r="I91" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>47576291924.25</v>
       </c>
       <c r="J91" s="5">
-        <f ca="1">ROUND(IF($C91&gt;=userRetirementAge, IF($I91&gt;0, $I91*annualEffectivePostRetirementROI, 0), IF($I91&gt;0, $I91*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>5709155031</v>
       </c>
       <c r="K91" s="6">
-        <f ca="1">ROUND(I91+J91, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>53285446955</v>
       </c>
     </row>
     <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2107</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2108</v>
       </c>
       <c r="C92" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>140</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>117</v>
       </c>
       <c r="D92" s="5">
-        <f ca="1">ROUND(K91, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>53285446955</v>
       </c>
       <c r="E92" s="14">
-        <f ca="1">ROUND(IF($C92&gt;userRetirementAge, IF($D92&gt;0,-FV(annualChangeInSWP, $C92-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E91+E91*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-7821486</v>
       </c>
       <c r="F92" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C92)</f>
@@ -5062,38 +5062,38 @@
         <v/>
       </c>
       <c r="H92" s="5">
-        <f ca="1">IF(AND($C92&gt;userRetirementAge, SUM($E92, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E92, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>812060.75</v>
       </c>
       <c r="I92" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>53276813408.25</v>
       </c>
       <c r="J92" s="5">
-        <f ca="1">ROUND(IF($C92&gt;=userRetirementAge, IF($I92&gt;0, $I92*annualEffectivePostRetirementROI, 0), IF($I92&gt;0, $I92*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>6393217609</v>
       </c>
       <c r="K92" s="6">
-        <f ca="1">ROUND(I92+J92, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>59670031017</v>
       </c>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B93" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2108</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2109</v>
       </c>
       <c r="C93" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>141</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>118</v>
       </c>
       <c r="D93" s="5">
-        <f ca="1">ROUND(K92, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>59670031017</v>
       </c>
       <c r="E93" s="14">
-        <f ca="1">ROUND(IF($C93&gt;userRetirementAge, IF($D93&gt;0,-FV(annualChangeInSWP, $C93-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E92+E92*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-7899701</v>
       </c>
       <c r="F93" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C93)</f>
@@ -5104,38 +5104,38 @@
         <v/>
       </c>
       <c r="H93" s="5">
-        <f ca="1">IF(AND($C93&gt;userRetirementAge, SUM($E93, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E93, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>821837.625</v>
       </c>
       <c r="I93" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>59661309478.375</v>
       </c>
       <c r="J93" s="5">
-        <f ca="1">ROUND(IF($C93&gt;=userRetirementAge, IF($I93&gt;0, $I93*annualEffectivePostRetirementROI, 0), IF($I93&gt;0, $I93*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>7159357137</v>
       </c>
       <c r="K93" s="6">
-        <f ca="1">ROUND(I93+J93, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>66820666615</v>
       </c>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B94" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2109</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2110</v>
       </c>
       <c r="C94" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>142</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>119</v>
       </c>
       <c r="D94" s="5">
-        <f ca="1">ROUND(K93, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>66820666615</v>
       </c>
       <c r="E94" s="14">
-        <f ca="1">ROUND(IF($C94&gt;userRetirementAge, IF($D94&gt;0,-FV(annualChangeInSWP, $C94-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E93+E93*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-7978698</v>
       </c>
       <c r="F94" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C94)</f>
@@ -5146,38 +5146,38 @@
         <v/>
       </c>
       <c r="H94" s="5">
-        <f ca="1">IF(AND($C94&gt;userRetirementAge, SUM($E94, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E94, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>831712.25</v>
       </c>
       <c r="I94" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>66811856204.75</v>
       </c>
       <c r="J94" s="5">
-        <f ca="1">ROUND(IF($C94&gt;=userRetirementAge, IF($I94&gt;0, $I94*annualEffectivePostRetirementROI, 0), IF($I94&gt;0, $I94*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>8017422745</v>
       </c>
       <c r="K94" s="6">
-        <f ca="1">ROUND(I94+J94, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>74829278950</v>
       </c>
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B95" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2110</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2111</v>
       </c>
       <c r="C95" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>143</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>120</v>
       </c>
       <c r="D95" s="5">
-        <f ca="1">ROUND(K94, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>74829278950</v>
       </c>
       <c r="E95" s="14">
-        <f ca="1">ROUND(IF($C95&gt;userRetirementAge, IF($D95&gt;0,-FV(annualChangeInSWP, $C95-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E94+E94*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-8058485</v>
       </c>
       <c r="F95" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C95)</f>
@@ -5188,38 +5188,38 @@
         <v/>
       </c>
       <c r="H95" s="5">
-        <f ca="1">IF(AND($C95&gt;userRetirementAge, SUM($E95, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E95, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>841685.625</v>
       </c>
       <c r="I95" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>74820378779.375</v>
       </c>
       <c r="J95" s="5">
-        <f ca="1">ROUND(IF($C95&gt;=userRetirementAge, IF($I95&gt;0, $I95*annualEffectivePostRetirementROI, 0), IF($I95&gt;0, $I95*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>8978445454</v>
       </c>
       <c r="K95" s="6">
-        <f ca="1">ROUND(I95+J95, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>83798824233</v>
       </c>
     </row>
     <row r="96" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B96" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2111</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2112</v>
       </c>
       <c r="C96" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>144</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>121</v>
       </c>
       <c r="D96" s="5">
-        <f ca="1">ROUND(K95, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>83798824233</v>
       </c>
       <c r="E96" s="14">
-        <f ca="1">ROUND(IF($C96&gt;userRetirementAge, IF($D96&gt;0,-FV(annualChangeInSWP, $C96-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E95+E95*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-8139070</v>
       </c>
       <c r="F96" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C96)</f>
@@ -5230,38 +5230,38 @@
         <v/>
       </c>
       <c r="H96" s="5">
-        <f ca="1">IF(AND($C96&gt;userRetirementAge, SUM($E96, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E96, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>851758.75</v>
       </c>
       <c r="I96" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>83789833404.25</v>
       </c>
       <c r="J96" s="5">
-        <f ca="1">ROUND(IF($C96&gt;=userRetirementAge, IF($I96&gt;0, $I96*annualEffectivePostRetirementROI, 0), IF($I96&gt;0, $I96*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>10054780009</v>
       </c>
       <c r="K96" s="6">
-        <f ca="1">ROUND(I96+J96, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>93844613413</v>
       </c>
     </row>
     <row r="97" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B97" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2112</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2113</v>
       </c>
       <c r="C97" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>145</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>122</v>
       </c>
       <c r="D97" s="5">
-        <f ca="1">ROUND(K96, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>93844613413</v>
       </c>
       <c r="E97" s="14">
-        <f ca="1">ROUND(IF($C97&gt;userRetirementAge, IF($D97&gt;0,-FV(annualChangeInSWP, $C97-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E96+E96*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-8220461</v>
       </c>
       <c r="F97" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C97)</f>
@@ -5272,38 +5272,38 @@
         <v/>
       </c>
       <c r="H97" s="5">
-        <f ca="1">IF(AND($C97&gt;userRetirementAge, SUM($E97, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E97, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>861932.625</v>
       </c>
       <c r="I97" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>93835531019.375</v>
       </c>
       <c r="J97" s="5">
-        <f ca="1">ROUND(IF($C97&gt;=userRetirementAge, IF($I97&gt;0, $I97*annualEffectivePostRetirementROI, 0), IF($I97&gt;0, $I97*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>11260263722</v>
       </c>
       <c r="K97" s="6">
-        <f ca="1">ROUND(I97+J97, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>105095794741</v>
       </c>
     </row>
     <row r="98" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B98" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2113</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2114</v>
       </c>
       <c r="C98" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>146</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>123</v>
       </c>
       <c r="D98" s="5">
-        <f ca="1">ROUND(K97, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>105095794741</v>
       </c>
       <c r="E98" s="14">
-        <f ca="1">ROUND(IF($C98&gt;userRetirementAge, IF($D98&gt;0,-FV(annualChangeInSWP, $C98-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E97+E97*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-8302665</v>
       </c>
       <c r="F98" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C98)</f>
@@ -5314,38 +5314,38 @@
         <v/>
       </c>
       <c r="H98" s="5">
-        <f ca="1">IF(AND($C98&gt;userRetirementAge, SUM($E98, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E98, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>872208.125</v>
       </c>
       <c r="I98" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>105086619867.875</v>
       </c>
       <c r="J98" s="5">
-        <f ca="1">ROUND(IF($C98&gt;=userRetirementAge, IF($I98&gt;0, $I98*annualEffectivePostRetirementROI, 0), IF($I98&gt;0, $I98*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>12610394384</v>
       </c>
       <c r="K98" s="6">
-        <f ca="1">ROUND(I98+J98, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>117697014252</v>
       </c>
     </row>
     <row r="99" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B99" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2114</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2115</v>
       </c>
       <c r="C99" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>147</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>124</v>
       </c>
       <c r="D99" s="5">
-        <f ca="1">ROUND(K98, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>117697014252</v>
       </c>
       <c r="E99" s="14">
-        <f ca="1">ROUND(IF($C99&gt;userRetirementAge, IF($D99&gt;0,-FV(annualChangeInSWP, $C99-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E98+E98*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-8385692</v>
       </c>
       <c r="F99" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C99)</f>
@@ -5356,38 +5356,38 @@
         <v/>
       </c>
       <c r="H99" s="5">
-        <f ca="1">IF(AND($C99&gt;userRetirementAge, SUM($E99, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E99, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>882586.5</v>
       </c>
       <c r="I99" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>117687745973.5</v>
       </c>
       <c r="J99" s="5">
-        <f ca="1">ROUND(IF($C99&gt;=userRetirementAge, IF($I99&gt;0, $I99*annualEffectivePostRetirementROI, 0), IF($I99&gt;0, $I99*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>14122529517</v>
       </c>
       <c r="K99" s="6">
-        <f ca="1">ROUND(I99+J99, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>131810275491</v>
       </c>
     </row>
     <row r="100" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B100" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2115</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2116</v>
       </c>
       <c r="C100" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>148</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>125</v>
       </c>
       <c r="D100" s="5">
-        <f ca="1">ROUND(K99, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>131810275491</v>
       </c>
       <c r="E100" s="14">
-        <f ca="1">ROUND(IF($C100&gt;userRetirementAge, IF($D100&gt;0,-FV(annualChangeInSWP, $C100-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E99+E99*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-8469549</v>
       </c>
       <c r="F100" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C100)</f>
@@ -5398,38 +5398,38 @@
         <v/>
       </c>
       <c r="H100" s="5">
-        <f ca="1">IF(AND($C100&gt;userRetirementAge, SUM($E100, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E100, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>893068.625</v>
       </c>
       <c r="I100" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>131800912873.375</v>
       </c>
       <c r="J100" s="5">
-        <f ca="1">ROUND(IF($C100&gt;=userRetirementAge, IF($I100&gt;0, $I100*annualEffectivePostRetirementROI, 0), IF($I100&gt;0, $I100*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>15816109545</v>
       </c>
       <c r="K100" s="6">
-        <f ca="1">ROUND(I100+J100, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>147617022418</v>
       </c>
     </row>
     <row r="101" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B101" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2116</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2117</v>
       </c>
       <c r="C101" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>149</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>126</v>
       </c>
       <c r="D101" s="5">
-        <f ca="1">ROUND(K100, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>147617022418</v>
       </c>
       <c r="E101" s="14">
-        <f ca="1">ROUND(IF($C101&gt;userRetirementAge, IF($D101&gt;0,-FV(annualChangeInSWP, $C101-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E100+E100*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-8554244</v>
       </c>
       <c r="F101" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C101)</f>
@@ -5440,38 +5440,38 @@
         <v/>
       </c>
       <c r="H101" s="5">
-        <f ca="1">IF(AND($C101&gt;userRetirementAge, SUM($E101, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E101, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>903655.5</v>
       </c>
       <c r="I101" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>147607564518.5</v>
       </c>
       <c r="J101" s="5">
-        <f ca="1">ROUND(IF($C101&gt;=userRetirementAge, IF($I101&gt;0, $I101*annualEffectivePostRetirementROI, 0), IF($I101&gt;0, $I101*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>17712907742</v>
       </c>
       <c r="K101" s="6">
-        <f ca="1">ROUND(I101+J101, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>165320472261</v>
       </c>
     </row>
     <row r="102" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B102" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2117</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2118</v>
       </c>
       <c r="C102" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>150</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>127</v>
       </c>
       <c r="D102" s="5">
-        <f ca="1">ROUND(K101, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>165320472261</v>
       </c>
       <c r="E102" s="14">
-        <f ca="1">ROUND(IF($C102&gt;userRetirementAge, IF($D102&gt;0,-FV(annualChangeInSWP, $C102-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E101+E101*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-8639787</v>
       </c>
       <c r="F102" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C102)</f>
@@ -5482,38 +5482,38 @@
         <v/>
       </c>
       <c r="H102" s="5">
-        <f ca="1">IF(AND($C102&gt;userRetirementAge, SUM($E102, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E102, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>914348.375</v>
       </c>
       <c r="I102" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>165310918125.625</v>
       </c>
       <c r="J102" s="5">
-        <f ca="1">ROUND(IF($C102&gt;=userRetirementAge, IF($I102&gt;0, $I102*annualEffectivePostRetirementROI, 0), IF($I102&gt;0, $I102*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>19837310175</v>
       </c>
       <c r="K102" s="6">
-        <f ca="1">ROUND(I102+J102, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>185148228301</v>
       </c>
     </row>
     <row r="103" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B103" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2118</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2119</v>
       </c>
       <c r="C103" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>151</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>128</v>
       </c>
       <c r="D103" s="5">
-        <f ca="1">ROUND(K102, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>185148228301</v>
       </c>
       <c r="E103" s="14">
-        <f ca="1">ROUND(IF($C103&gt;userRetirementAge, IF($D103&gt;0,-FV(annualChangeInSWP, $C103-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E102+E102*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-8726185</v>
       </c>
       <c r="F103" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C103)</f>
@@ -5524,38 +5524,38 @@
         <v/>
       </c>
       <c r="H103" s="5">
-        <f ca="1">IF(AND($C103&gt;userRetirementAge, SUM($E103, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E103, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>925148.125</v>
       </c>
       <c r="I103" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>185138576967.875</v>
       </c>
       <c r="J103" s="5">
-        <f ca="1">ROUND(IF($C103&gt;=userRetirementAge, IF($I103&gt;0, $I103*annualEffectivePostRetirementROI, 0), IF($I103&gt;0, $I103*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>22216629236</v>
       </c>
       <c r="K103" s="6">
-        <f ca="1">ROUND(I103+J103, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>207355206204</v>
       </c>
     </row>
     <row r="104" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B104" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2119</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2120</v>
       </c>
       <c r="C104" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>152</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>129</v>
       </c>
       <c r="D104" s="5">
-        <f ca="1">ROUND(K103, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>207355206204</v>
       </c>
       <c r="E104" s="14">
-        <f ca="1">ROUND(IF($C104&gt;userRetirementAge, IF($D104&gt;0,-FV(annualChangeInSWP, $C104-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E103+E103*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-8813447</v>
       </c>
       <c r="F104" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C104)</f>
@@ -5566,38 +5566,38 @@
         <v/>
       </c>
       <c r="H104" s="5">
-        <f ca="1">IF(AND($C104&gt;userRetirementAge, SUM($E104, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E104, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>936055.875</v>
       </c>
       <c r="I104" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>207345456701.125</v>
       </c>
       <c r="J104" s="5">
-        <f ca="1">ROUND(IF($C104&gt;=userRetirementAge, IF($I104&gt;0, $I104*annualEffectivePostRetirementROI, 0), IF($I104&gt;0, $I104*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>24881454804</v>
       </c>
       <c r="K104" s="6">
-        <f ca="1">ROUND(I104+J104, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>232226911505</v>
       </c>
     </row>
     <row r="105" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B105" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2120</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2121</v>
       </c>
       <c r="C105" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>153</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>130</v>
       </c>
       <c r="D105" s="5">
-        <f ca="1">ROUND(K104, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>232226911505</v>
       </c>
       <c r="E105" s="14">
-        <f ca="1">ROUND(IF($C105&gt;userRetirementAge, IF($D105&gt;0,-FV(annualChangeInSWP, $C105-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E104+E104*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-8901581</v>
       </c>
       <c r="F105" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C105)</f>
@@ -5608,38 +5608,38 @@
         <v/>
       </c>
       <c r="H105" s="5">
-        <f ca="1">IF(AND($C105&gt;userRetirementAge, SUM($E105, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E105, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>947072.625</v>
       </c>
       <c r="I105" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>232217062851.375</v>
       </c>
       <c r="J105" s="5">
-        <f ca="1">ROUND(IF($C105&gt;=userRetirementAge, IF($I105&gt;0, $I105*annualEffectivePostRetirementROI, 0), IF($I105&gt;0, $I105*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>27866047542</v>
       </c>
       <c r="K105" s="6">
-        <f ca="1">ROUND(I105+J105, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ref="K105:K136" ca="1" si="23">ROUND(I105+J105, 0)</f>
+        <v>260083110393</v>
       </c>
     </row>
     <row r="106" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B106" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2121</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2122</v>
       </c>
       <c r="C106" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>154</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>131</v>
       </c>
       <c r="D106" s="5">
-        <f ca="1">ROUND(K105, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>260083110393</v>
       </c>
       <c r="E106" s="14">
-        <f ca="1">ROUND(IF($C106&gt;userRetirementAge, IF($D106&gt;0,-FV(annualChangeInSWP, $C106-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E105+E105*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-8990597</v>
       </c>
       <c r="F106" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C106)</f>
@@ -5650,38 +5650,38 @@
         <v/>
       </c>
       <c r="H106" s="5">
-        <f ca="1">IF(AND($C106&gt;userRetirementAge, SUM($E106, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E106, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>958199.625</v>
       </c>
       <c r="I106" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>260073161596.375</v>
       </c>
       <c r="J106" s="5">
-        <f ca="1">ROUND(IF($C106&gt;=userRetirementAge, IF($I106&gt;0, $I106*annualEffectivePostRetirementROI, 0), IF($I106&gt;0, $I106*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>31208779392</v>
       </c>
       <c r="K106" s="6">
-        <f ca="1">ROUND(I106+J106, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>291281940988</v>
       </c>
     </row>
     <row r="107" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B107" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2122</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2123</v>
       </c>
       <c r="C107" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>155</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>132</v>
       </c>
       <c r="D107" s="5">
-        <f ca="1">ROUND(K106, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>291281940988</v>
       </c>
       <c r="E107" s="14">
-        <f ca="1">ROUND(IF($C107&gt;userRetirementAge, IF($D107&gt;0,-FV(annualChangeInSWP, $C107-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E106+E106*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-9080503</v>
       </c>
       <c r="F107" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C107)</f>
@@ -5692,38 +5692,38 @@
         <v/>
       </c>
       <c r="H107" s="5">
-        <f ca="1">IF(AND($C107&gt;userRetirementAge, SUM($E107, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E107, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>969437.875</v>
       </c>
       <c r="I107" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>291271891047.125</v>
       </c>
       <c r="J107" s="5">
-        <f ca="1">ROUND(IF($C107&gt;=userRetirementAge, IF($I107&gt;0, $I107*annualEffectivePostRetirementROI, 0), IF($I107&gt;0, $I107*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>34952626926</v>
       </c>
       <c r="K107" s="6">
-        <f ca="1">ROUND(I107+J107, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>326224517973</v>
       </c>
     </row>
     <row r="108" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B108" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2123</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2124</v>
       </c>
       <c r="C108" s="4">
-        <f t="shared" ca="1" si="6"/>
-        <v>156</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>133</v>
       </c>
       <c r="D108" s="5">
-        <f ca="1">ROUND(K107, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>326224517973</v>
       </c>
       <c r="E108" s="14">
-        <f ca="1">ROUND(IF($C108&gt;userRetirementAge, IF($D108&gt;0,-FV(annualChangeInSWP, $C108-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E107+E107*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-9171308</v>
       </c>
       <c r="F108" s="5">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C108)</f>
@@ -5734,38 +5734,38 @@
         <v/>
       </c>
       <c r="H108" s="5">
-        <f ca="1">IF(AND($C108&gt;userRetirementAge, SUM($E108, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E108, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>980788.5</v>
       </c>
       <c r="I108" s="5">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>326214365876.5</v>
       </c>
       <c r="J108" s="5">
-        <f ca="1">ROUND(IF($C108&gt;=userRetirementAge, IF($I108&gt;0, $I108*annualEffectivePostRetirementROI, 0), IF($I108&gt;0, $I108*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>39145723905</v>
       </c>
       <c r="K108" s="6">
-        <f ca="1">ROUND(I108+J108, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>365360089782</v>
       </c>
     </row>
     <row r="109" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B109" s="7">
-        <f t="shared" ca="1" si="5"/>
-        <v>2124</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>2125</v>
       </c>
       <c r="C109" s="8">
-        <f t="shared" ca="1" si="6"/>
-        <v>157</v>
+        <f t="shared" ca="1" si="19"/>
+        <v>134</v>
       </c>
       <c r="D109" s="9">
-        <f ca="1">ROUND(K108, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="20"/>
+        <v>365360089782</v>
       </c>
       <c r="E109" s="37">
-        <f ca="1">ROUND(IF($C109&gt;userRetirementAge, IF($D109&gt;0,-FV(annualChangeInSWP, $C109-userRetirementAge-1, 0, -annualWithdrawalSWP_FV, 1), 0), E108+E108*(annualIncreaseInSavings)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>-9263021</v>
       </c>
       <c r="F109" s="9">
         <f ca="1">-SUMIFS('Input-Events'!H$4:H$106, 'Input-Events'!E$4:E$106, $C109)</f>
@@ -5776,64 +5776,50 @@
         <v/>
       </c>
       <c r="H109" s="9">
-        <f ca="1">IF(AND($C109&gt;userRetirementAge, SUM($E109, swpLTCGExemption, swpOtherTaxExemptions) &lt; 0), (-SUM($E109, swpLTCGExemption, swpOtherTaxExemptions))*swpLTCGTaxPercentage, 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>992252.625</v>
       </c>
       <c r="I109" s="9">
-        <f t="shared" ca="1" si="7"/>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>365349834508.375</v>
       </c>
       <c r="J109" s="9">
-        <f ca="1">ROUND(IF($C109&gt;=userRetirementAge, IF($I109&gt;0, $I109*annualEffectivePostRetirementROI, 0), IF($I109&gt;0, $I109*annualEffectiveROI, 0)), 0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>43841980141</v>
       </c>
       <c r="K109" s="10">
-        <f ca="1">ROUND(I109+J109, 0)</f>
-        <v>-1546418</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>409191814649</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
-  <conditionalFormatting sqref="I9:K109 B9:G109">
-    <cfRule type="expression" dxfId="10" priority="6">
+  <conditionalFormatting sqref="B9:K109">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>$C9&gt;userLifeExpectancyAge</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="7">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>$C9=userLifeExpectancyAge</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="10">
+    <cfRule type="expression" dxfId="4" priority="3">
       <formula>$C9=userRetirementAge</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="11">
+    <cfRule type="expression" dxfId="3" priority="4">
       <formula>IF($C9&gt;userRetirementAge, $C9&lt;userLifeExpectancyAge)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I9:I109 D9:F109">
-    <cfRule type="cellIs" dxfId="6" priority="15" operator="lessThan">
+  <conditionalFormatting sqref="D9:F109">
+    <cfRule type="cellIs" dxfId="2" priority="15" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H9:I109">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J9:K109">
-    <cfRule type="cellIs" dxfId="5" priority="14" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H9:H109">
-    <cfRule type="expression" dxfId="4" priority="1">
-      <formula>$C9&gt;userLifeExpectancyAge</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="2">
-      <formula>$C9=userLifeExpectancyAge</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="3">
-      <formula>$C9=userRetirementAge</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="4">
-      <formula>IF($C9&gt;userRetirementAge, $C9&lt;userLifeExpectancyAge)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H9:H109">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="14" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5873,7 +5859,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C81A75B6-952D-4F5A-A6D3-C8680062EE1E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C81A75B6-952D-4F5A-A6D3-C8680062EE1E}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:N38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5883,7 +5869,7 @@
     <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="29.140625" customWidth="1"/>
     <col min="5" max="5" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="39.140625" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="34.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -5920,18 +5906,18 @@
     </row>
     <row r="6" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="73" t="s">
+      <c r="B7" s="84" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="74"/>
-      <c r="E7" s="73" t="s">
+      <c r="C7" s="85"/>
+      <c r="E7" s="84" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="74"/>
+      <c r="F7" s="85"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B8" s="38" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C8" s="55"/>
       <c r="E8" s="1"/>
@@ -5951,7 +5937,7 @@
       </c>
       <c r="F9" s="46">
         <f ca="1">DATEDIF(C10, TODAY(), "y")</f>
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="M9" s="45"/>
       <c r="N9" s="21"/>
@@ -5961,14 +5947,14 @@
         <v>3</v>
       </c>
       <c r="C10" s="53">
-        <v>24838</v>
+        <v>33604</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="47">
         <f>userMonthlyExpenses</f>
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="M10" s="45"/>
       <c r="N10" s="22"/>
@@ -5978,7 +5964,7 @@
         <v>88</v>
       </c>
       <c r="C11" s="54">
-        <v>120000</v>
+        <v>100000</v>
       </c>
       <c r="E11" s="26"/>
       <c r="F11" s="32"/>
@@ -5990,14 +5976,14 @@
         <v>5</v>
       </c>
       <c r="C12" s="54">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="E12" s="26" t="s">
         <v>19</v>
       </c>
       <c r="F12" s="47">
         <f>ROUND(12*(userIncome-userMonthlyExpenses),0)</f>
-        <v>1200000</v>
+        <v>600000</v>
       </c>
       <c r="M12" s="45"/>
       <c r="N12" s="20"/>
@@ -6014,18 +6000,18 @@
       </c>
       <c r="F13" s="48">
         <f>$C$16-SUM($C$17:$C$19)</f>
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="31"/>
-      <c r="C14" s="86"/>
+      <c r="C14" s="83"/>
       <c r="E14" s="26" t="s">
         <v>73</v>
       </c>
       <c r="F14" s="48">
         <f>$C$24-SUM($C$25:$C$27)</f>
-        <v>7.9999999999999988E-2</v>
+        <v>0.12000000000000001</v>
       </c>
       <c r="M14" s="45"/>
       <c r="N14" s="23"/>
@@ -6044,15 +6030,15 @@
       <c r="B16" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="82">
-        <v>0.1</v>
+      <c r="C16" s="79">
+        <v>0.12</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F16" s="47">
         <f ca="1">ROUND(FV($C$25, userRetirementAge-userAge, 0, -annualAmountSWP, 1), 0)</f>
-        <v>1373880</v>
+        <v>4480148</v>
       </c>
       <c r="M16" s="45"/>
       <c r="N16" s="23"/>
@@ -6061,7 +6047,7 @@
       <c r="B17" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="82">
+      <c r="C17" s="79">
         <v>0</v>
       </c>
       <c r="E17" s="26"/>
@@ -6073,7 +6059,7 @@
       <c r="B18" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="82">
+      <c r="C18" s="79">
         <v>0</v>
       </c>
       <c r="E18" s="26"/>
@@ -6085,7 +6071,7 @@
       <c r="B19" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="82">
+      <c r="C19" s="79">
         <v>0</v>
       </c>
       <c r="E19" s="26"/>
@@ -6101,7 +6087,7 @@
       <c r="B21" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="82">
+      <c r="C21" s="79">
         <v>0.05</v>
       </c>
       <c r="E21" s="26"/>
@@ -6109,7 +6095,7 @@
     </row>
     <row r="22" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="31"/>
-      <c r="C22" s="86"/>
+      <c r="C22" s="83"/>
       <c r="E22" s="26"/>
       <c r="F22" s="32"/>
     </row>
@@ -6127,8 +6113,8 @@
       <c r="B24" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="82">
-        <v>0.15</v>
+      <c r="C24" s="79">
+        <v>0.17</v>
       </c>
       <c r="E24" s="31"/>
       <c r="F24" s="49"/>
@@ -6138,8 +6124,8 @@
       <c r="B25" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="C25" s="82">
-        <v>7.0000000000000007E-2</v>
+      <c r="C25" s="79">
+        <v>0.05</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -6147,7 +6133,7 @@
       <c r="B26" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="C26" s="82">
+      <c r="C26" s="79">
         <v>0</v>
       </c>
       <c r="M26" s="45"/>
@@ -6158,7 +6144,7 @@
       <c r="B27" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="82">
+      <c r="C27" s="79">
         <v>0</v>
       </c>
       <c r="M27" s="45"/>
@@ -6187,14 +6173,14 @@
       <c r="B30" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="C30" s="82">
+      <c r="C30" s="79">
         <v>0.01</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4"/>
       <c r="B31" s="31"/>
-      <c r="C31" s="86"/>
+      <c r="C31" s="83"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
@@ -6208,7 +6194,7 @@
         <v>55</v>
       </c>
       <c r="C33" s="56">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6220,17 +6206,17 @@
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="83" t="s">
+      <c r="B35" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="C35" s="84"/>
+      <c r="C35" s="81"/>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="26" t="s">
         <v>92</v>
       </c>
       <c r="C36" s="54">
-        <v>700000</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
@@ -6245,7 +6231,7 @@
       <c r="B38" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="C38" s="85">
+      <c r="C38" s="82">
         <v>0.125</v>
       </c>
     </row>
@@ -6257,6 +6243,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -6279,13 +6266,13 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="I1" s="58" t="str">
         <f>CONCATENATE("*Make sure total expense doesn't exceed monthly income of ", userMonthlyIncome )</f>
-        <v>*Make sure total expense doesn't exceed monthly income of 120000</v>
-      </c>
-      <c r="L1" s="75" t="s">
+        <v>*Make sure total expense doesn't exceed monthly income of 100000</v>
+      </c>
+      <c r="L1" s="86" t="s">
         <v>62</v>
       </c>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
+      <c r="M1" s="86"/>
+      <c r="N1" s="86"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L2" s="59"/>
@@ -6298,7 +6285,7 @@
       </c>
       <c r="B3" s="61">
         <f>SUM(E4:E45)</f>
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="D3" s="39" t="s">
         <v>40</v>
@@ -6340,7 +6327,7 @@
         <v>42</v>
       </c>
       <c r="E5" s="13">
-        <v>3000</v>
+        <v>30000</v>
       </c>
       <c r="L5" s="59" t="s">
         <v>65</v>
@@ -6412,7 +6399,7 @@
         <v>47</v>
       </c>
       <c r="E9" s="13">
-        <v>1000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -6600,7 +6587,7 @@
       </c>
       <c r="B3" s="61">
         <f>SUMIF($F$4:$F$106, "&gt;=0")</f>
-        <v>7100000</v>
+        <v>7000000</v>
       </c>
       <c r="D3" s="39" t="s">
         <v>10</v>
@@ -6624,18 +6611,18 @@
       </c>
       <c r="B4" s="61">
         <f>-SUMIF($F$4:$F$106, "&lt;0")</f>
-        <v>12100000</v>
+        <v>13000000</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="13"/>
-      <c r="G4" s="76">
-        <v>0</v>
-      </c>
-      <c r="H4" s="77">
-        <f>IF(AND($G4 &gt; 0, $E4 &gt; 0), CEILING(FV($G4, $E4-userAge, 0, -$F4, 1), 1000), $F4)</f>
+      <c r="G4" s="73">
+        <v>0</v>
+      </c>
+      <c r="H4" s="74">
+        <f t="shared" ref="H4:H35" si="0">IF(AND($G4 &gt; 0, $E4 &gt; 0), CEILING(FV($G4, $E4-userAge, 0, -$F4, 1), 1000), $F4)</f>
         <v>0</v>
       </c>
     </row>
@@ -6645,11 +6632,11 @@
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="13"/>
-      <c r="G5" s="76">
+      <c r="G5" s="73">
         <v>0.1</v>
       </c>
-      <c r="H5" s="77">
-        <f>IF(AND($G5 &gt; 0, $E5 &gt; 0), CEILING(FV($G5, $E5-userAge, 0, -$F5, 1), 1000), $F5)</f>
+      <c r="H5" s="74">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -6659,11 +6646,11 @@
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="13"/>
-      <c r="G6" s="76">
-        <v>0</v>
-      </c>
-      <c r="H6" s="77">
-        <f>IF(AND($G6 &gt; 0, $E6 &gt; 0), CEILING(FV($G6, $E6-userAge, 0, -$F6, 1), 1000), $F6)</f>
+      <c r="G6" s="73">
+        <v>0</v>
+      </c>
+      <c r="H6" s="74">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -6672,35 +6659,31 @@
         <v>8</v>
       </c>
       <c r="E7" s="12">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F7" s="13">
         <v>1000000</v>
       </c>
-      <c r="G7" s="76">
+      <c r="G7" s="73">
         <v>0.05</v>
       </c>
-      <c r="H7" s="77">
-        <f ca="1">IF(AND($G7 &gt; 0, $E7 &gt; 0), CEILING(FV($G7, $E7-userAge, 0, -$F7, 1), 1000), $F7)</f>
-        <v>359000</v>
+      <c r="H7" s="74">
+        <f t="shared" ca="1" si="0"/>
+        <v>1277000</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D8" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="12">
-        <v>34</v>
-      </c>
-      <c r="F8" s="13">
-        <v>100000</v>
-      </c>
-      <c r="G8" s="76">
-        <v>0</v>
-      </c>
-      <c r="H8" s="77">
-        <f>IF(AND($G8 &gt; 0, $E8 &gt; 0), CEILING(FV($G8, $E8-userAge, 0, -$F8, 1), 1000), $F8)</f>
-        <v>100000</v>
+      <c r="E8" s="12"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="73">
+        <v>0</v>
+      </c>
+      <c r="H8" s="74">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -6708,17 +6691,17 @@
         <v>29</v>
       </c>
       <c r="E9" s="12">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F9" s="13">
         <v>500000</v>
       </c>
-      <c r="G9" s="76">
-        <v>0</v>
-      </c>
-      <c r="H9" s="77">
-        <f>IF(AND($G9 &gt; 0, $E9 &gt; 0), CEILING(FV($G9, $E9-userAge, 0, -$F9, 1), 1000), $F9)</f>
-        <v>500000</v>
+      <c r="G9" s="73">
+        <v>0.02</v>
+      </c>
+      <c r="H9" s="74">
+        <f t="shared" ca="1" si="0"/>
+        <v>521000</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -6727,11 +6710,11 @@
       </c>
       <c r="E10" s="12"/>
       <c r="F10" s="13"/>
-      <c r="G10" s="76">
-        <v>0</v>
-      </c>
-      <c r="H10" s="77">
-        <f>IF(AND($G10 &gt; 0, $E10 &gt; 0), CEILING(FV($G10, $E10-userAge, 0, -$F10, 1), 1000), $F10)</f>
+      <c r="G10" s="73">
+        <v>0</v>
+      </c>
+      <c r="H10" s="74">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -6740,17 +6723,17 @@
         <v>9</v>
       </c>
       <c r="E11" s="12">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F11" s="13">
         <v>5000000</v>
       </c>
-      <c r="G11" s="76">
-        <v>0.05</v>
-      </c>
-      <c r="H11" s="77">
-        <f ca="1">IF(AND($G11 &gt; 0, $E11 &gt; 0), CEILING(FV($G11, $E11-userAge, 0, -$F11, 1), 1000), $F11)</f>
-        <v>2291000</v>
+      <c r="G11" s="73">
+        <v>0.03</v>
+      </c>
+      <c r="H11" s="74">
+        <f t="shared" ca="1" si="0"/>
+        <v>8265000</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -6758,16 +6741,16 @@
         <v>24</v>
       </c>
       <c r="E12" s="12">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F12" s="13">
         <v>500000</v>
       </c>
-      <c r="G12" s="76">
-        <v>0</v>
-      </c>
-      <c r="H12" s="77">
-        <f>IF(AND($G12 &gt; 0, $E12 &gt; 0), CEILING(FV($G12, $E12-userAge, 0, -$F12, 1), 1000), $F12)</f>
+      <c r="G12" s="73">
+        <v>0</v>
+      </c>
+      <c r="H12" s="74">
+        <f t="shared" si="0"/>
         <v>500000</v>
       </c>
     </row>
@@ -6777,11 +6760,11 @@
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="13"/>
-      <c r="G13" s="76">
-        <v>0</v>
-      </c>
-      <c r="H13" s="77">
-        <f>IF(AND($G13 &gt; 0, $E13 &gt; 0), CEILING(FV($G13, $E13-userAge, 0, -$F13, 1), 1000), $F13)</f>
+      <c r="G13" s="73">
+        <v>0</v>
+      </c>
+      <c r="H13" s="74">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -6791,11 +6774,11 @@
       </c>
       <c r="E14" s="12"/>
       <c r="F14" s="13"/>
-      <c r="G14" s="76">
-        <v>0</v>
-      </c>
-      <c r="H14" s="77">
-        <f>IF(AND($G14 &gt; 0, $E14 &gt; 0), CEILING(FV($G14, $E14-userAge, 0, -$F14, 1), 1000), $F14)</f>
+      <c r="G14" s="73">
+        <v>0</v>
+      </c>
+      <c r="H14" s="74">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -6805,11 +6788,11 @@
       </c>
       <c r="E15" s="12"/>
       <c r="F15" s="13"/>
-      <c r="G15" s="76">
-        <v>0</v>
-      </c>
-      <c r="H15" s="77">
-        <f>IF(AND($G15 &gt; 0, $E15 &gt; 0), CEILING(FV($G15, $E15-userAge, 0, -$F15, 1), 1000), $F15)</f>
+      <c r="G15" s="73">
+        <v>0</v>
+      </c>
+      <c r="H15" s="74">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -6819,11 +6802,11 @@
       </c>
       <c r="E16" s="12"/>
       <c r="F16" s="13"/>
-      <c r="G16" s="76">
-        <v>0</v>
-      </c>
-      <c r="H16" s="77">
-        <f>IF(AND($G16 &gt; 0, $E16 &gt; 0), CEILING(FV($G16, $E16-userAge, 0, -$F16, 1), 1000), $F16)</f>
+      <c r="G16" s="73">
+        <v>0</v>
+      </c>
+      <c r="H16" s="74">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -6833,11 +6816,11 @@
       </c>
       <c r="E17" s="12"/>
       <c r="F17" s="13"/>
-      <c r="G17" s="76">
-        <v>0</v>
-      </c>
-      <c r="H17" s="77">
-        <f>IF(AND($G17 &gt; 0, $E17 &gt; 0), CEILING(FV($G17, $E17-userAge, 0, -$F17, 1), 1000), $F17)</f>
+      <c r="G17" s="73">
+        <v>0</v>
+      </c>
+      <c r="H17" s="74">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -6847,11 +6830,11 @@
       </c>
       <c r="E18" s="12"/>
       <c r="F18" s="13"/>
-      <c r="G18" s="76">
-        <v>0</v>
-      </c>
-      <c r="H18" s="77">
-        <f>IF(AND($G18 &gt; 0, $E18 &gt; 0), CEILING(FV($G18, $E18-userAge, 0, -$F18, 1), 1000), $F18)</f>
+      <c r="G18" s="73">
+        <v>0</v>
+      </c>
+      <c r="H18" s="74">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -6861,11 +6844,11 @@
       </c>
       <c r="E19" s="12"/>
       <c r="F19" s="13"/>
-      <c r="G19" s="76">
-        <v>0</v>
-      </c>
-      <c r="H19" s="77">
-        <f>IF(AND($G19 &gt; 0, $E19 &gt; 0), CEILING(FV($G19, $E19-userAge, 0, -$F19, 1), 1000), $F19)</f>
+      <c r="G19" s="73">
+        <v>0</v>
+      </c>
+      <c r="H19" s="74">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -6873,11 +6856,11 @@
       <c r="D20" s="11"/>
       <c r="E20" s="12"/>
       <c r="F20" s="13"/>
-      <c r="G20" s="76">
-        <v>0</v>
-      </c>
-      <c r="H20" s="77">
-        <f>IF(AND($G20 &gt; 0, $E20 &gt; 0), CEILING(FV($G20, $E20-userAge, 0, -$F20, 1), 1000), $F20)</f>
+      <c r="G20" s="73">
+        <v>0</v>
+      </c>
+      <c r="H20" s="74">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -6885,11 +6868,11 @@
       <c r="D21" s="11"/>
       <c r="E21" s="12"/>
       <c r="F21" s="13"/>
-      <c r="G21" s="76">
-        <v>0</v>
-      </c>
-      <c r="H21" s="77">
-        <f>IF(AND($G21 &gt; 0, $E21 &gt; 0), CEILING(FV($G21, $E21-userAge, 0, -$F21, 1), 1000), $F21)</f>
+      <c r="G21" s="73">
+        <v>0</v>
+      </c>
+      <c r="H21" s="74">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -6897,11 +6880,11 @@
       <c r="D22" s="11"/>
       <c r="E22" s="12"/>
       <c r="F22" s="13"/>
-      <c r="G22" s="76">
-        <v>0</v>
-      </c>
-      <c r="H22" s="77">
-        <f>IF(AND($G22 &gt; 0, $E22 &gt; 0), CEILING(FV($G22, $E22-userAge, 0, -$F22, 1), 1000), $F22)</f>
+      <c r="G22" s="73">
+        <v>0</v>
+      </c>
+      <c r="H22" s="74">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -6909,11 +6892,11 @@
       <c r="D23" s="11"/>
       <c r="E23" s="12"/>
       <c r="F23" s="13"/>
-      <c r="G23" s="76">
-        <v>0</v>
-      </c>
-      <c r="H23" s="77">
-        <f>IF(AND($G23 &gt; 0, $E23 &gt; 0), CEILING(FV($G23, $E23-userAge, 0, -$F23, 1), 1000), $F23)</f>
+      <c r="G23" s="73">
+        <v>0</v>
+      </c>
+      <c r="H23" s="74">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -6921,11 +6904,11 @@
       <c r="D24" s="11"/>
       <c r="E24" s="12"/>
       <c r="F24" s="13"/>
-      <c r="G24" s="76">
-        <v>0</v>
-      </c>
-      <c r="H24" s="77">
-        <f>IF(AND($G24 &gt; 0, $E24 &gt; 0), CEILING(FV($G24, $E24-userAge, 0, -$F24, 1), 1000), $F24)</f>
+      <c r="G24" s="73">
+        <v>0</v>
+      </c>
+      <c r="H24" s="74">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -6933,11 +6916,11 @@
       <c r="D25" s="11"/>
       <c r="E25" s="12"/>
       <c r="F25" s="13"/>
-      <c r="G25" s="76">
-        <v>0</v>
-      </c>
-      <c r="H25" s="77">
-        <f>IF(AND($G25 &gt; 0, $E25 &gt; 0), CEILING(FV($G25, $E25-userAge, 0, -$F25, 1), 1000), $F25)</f>
+      <c r="G25" s="73">
+        <v>0</v>
+      </c>
+      <c r="H25" s="74">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -6945,11 +6928,11 @@
       <c r="D26" s="11"/>
       <c r="E26" s="12"/>
       <c r="F26" s="13"/>
-      <c r="G26" s="76">
-        <v>0</v>
-      </c>
-      <c r="H26" s="77">
-        <f>IF(AND($G26 &gt; 0, $E26 &gt; 0), CEILING(FV($G26, $E26-userAge, 0, -$F26, 1), 1000), $F26)</f>
+      <c r="G26" s="73">
+        <v>0</v>
+      </c>
+      <c r="H26" s="74">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -6957,11 +6940,11 @@
       <c r="D27" s="11"/>
       <c r="E27" s="12"/>
       <c r="F27" s="13"/>
-      <c r="G27" s="76">
-        <v>0</v>
-      </c>
-      <c r="H27" s="77">
-        <f>IF(AND($G27 &gt; 0, $E27 &gt; 0), CEILING(FV($G27, $E27-userAge, 0, -$F27, 1), 1000), $F27)</f>
+      <c r="G27" s="73">
+        <v>0</v>
+      </c>
+      <c r="H27" s="74">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -6969,11 +6952,11 @@
       <c r="D28" s="11"/>
       <c r="E28" s="12"/>
       <c r="F28" s="13"/>
-      <c r="G28" s="76">
-        <v>0</v>
-      </c>
-      <c r="H28" s="77">
-        <f>IF(AND($G28 &gt; 0, $E28 &gt; 0), CEILING(FV($G28, $E28-userAge, 0, -$F28, 1), 1000), $F28)</f>
+      <c r="G28" s="73">
+        <v>0</v>
+      </c>
+      <c r="H28" s="74">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -6981,11 +6964,11 @@
       <c r="D29" s="11"/>
       <c r="E29" s="12"/>
       <c r="F29" s="13"/>
-      <c r="G29" s="76">
-        <v>0</v>
-      </c>
-      <c r="H29" s="77">
-        <f>IF(AND($G29 &gt; 0, $E29 &gt; 0), CEILING(FV($G29, $E29-userAge, 0, -$F29, 1), 1000), $F29)</f>
+      <c r="G29" s="73">
+        <v>0</v>
+      </c>
+      <c r="H29" s="74">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -6993,11 +6976,11 @@
       <c r="D30" s="11"/>
       <c r="E30" s="12"/>
       <c r="F30" s="13"/>
-      <c r="G30" s="76">
-        <v>0</v>
-      </c>
-      <c r="H30" s="77">
-        <f>IF(AND($G30 &gt; 0, $E30 &gt; 0), CEILING(FV($G30, $E30-userAge, 0, -$F30, 1), 1000), $F30)</f>
+      <c r="G30" s="73">
+        <v>0</v>
+      </c>
+      <c r="H30" s="74">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -7005,11 +6988,11 @@
       <c r="D31" s="11"/>
       <c r="E31" s="12"/>
       <c r="F31" s="13"/>
-      <c r="G31" s="76">
-        <v>0</v>
-      </c>
-      <c r="H31" s="77">
-        <f>IF(AND($G31 &gt; 0, $E31 &gt; 0), CEILING(FV($G31, $E31-userAge, 0, -$F31, 1), 1000), $F31)</f>
+      <c r="G31" s="73">
+        <v>0</v>
+      </c>
+      <c r="H31" s="74">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -7017,11 +7000,11 @@
       <c r="D32" s="11"/>
       <c r="E32" s="12"/>
       <c r="F32" s="13"/>
-      <c r="G32" s="76">
-        <v>0</v>
-      </c>
-      <c r="H32" s="77">
-        <f>IF(AND($G32 &gt; 0, $E32 &gt; 0), CEILING(FV($G32, $E32-userAge, 0, -$F32, 1), 1000), $F32)</f>
+      <c r="G32" s="73">
+        <v>0</v>
+      </c>
+      <c r="H32" s="74">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -7029,11 +7012,11 @@
       <c r="D33" s="11"/>
       <c r="E33" s="12"/>
       <c r="F33" s="13"/>
-      <c r="G33" s="76">
-        <v>0</v>
-      </c>
-      <c r="H33" s="77">
-        <f>IF(AND($G33 &gt; 0, $E33 &gt; 0), CEILING(FV($G33, $E33-userAge, 0, -$F33, 1), 1000), $F33)</f>
+      <c r="G33" s="73">
+        <v>0</v>
+      </c>
+      <c r="H33" s="74">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -7041,11 +7024,11 @@
       <c r="D34" s="11"/>
       <c r="E34" s="12"/>
       <c r="F34" s="13"/>
-      <c r="G34" s="76">
-        <v>0</v>
-      </c>
-      <c r="H34" s="77">
-        <f>IF(AND($G34 &gt; 0, $E34 &gt; 0), CEILING(FV($G34, $E34-userAge, 0, -$F34, 1), 1000), $F34)</f>
+      <c r="G34" s="73">
+        <v>0</v>
+      </c>
+      <c r="H34" s="74">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -7053,11 +7036,11 @@
       <c r="D35" s="11"/>
       <c r="E35" s="12"/>
       <c r="F35" s="13"/>
-      <c r="G35" s="76">
-        <v>0</v>
-      </c>
-      <c r="H35" s="77">
-        <f>IF(AND($G35 &gt; 0, $E35 &gt; 0), CEILING(FV($G35, $E35-userAge, 0, -$F35, 1), 1000), $F35)</f>
+      <c r="G35" s="73">
+        <v>0</v>
+      </c>
+      <c r="H35" s="74">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -7065,11 +7048,11 @@
       <c r="D36" s="11"/>
       <c r="E36" s="12"/>
       <c r="F36" s="13"/>
-      <c r="G36" s="76">
-        <v>0</v>
-      </c>
-      <c r="H36" s="77">
-        <f>IF(AND($G36 &gt; 0, $E36 &gt; 0), CEILING(FV($G36, $E36-userAge, 0, -$F36, 1), 1000), $F36)</f>
+      <c r="G36" s="73">
+        <v>0</v>
+      </c>
+      <c r="H36" s="74">
+        <f t="shared" ref="H36:H67" si="1">IF(AND($G36 &gt; 0, $E36 &gt; 0), CEILING(FV($G36, $E36-userAge, 0, -$F36, 1), 1000), $F36)</f>
         <v>0</v>
       </c>
     </row>
@@ -7077,11 +7060,11 @@
       <c r="D37" s="11"/>
       <c r="E37" s="12"/>
       <c r="F37" s="13"/>
-      <c r="G37" s="76">
-        <v>0</v>
-      </c>
-      <c r="H37" s="77">
-        <f>IF(AND($G37 &gt; 0, $E37 &gt; 0), CEILING(FV($G37, $E37-userAge, 0, -$F37, 1), 1000), $F37)</f>
+      <c r="G37" s="73">
+        <v>0</v>
+      </c>
+      <c r="H37" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7089,11 +7072,11 @@
       <c r="D38" s="11"/>
       <c r="E38" s="12"/>
       <c r="F38" s="13"/>
-      <c r="G38" s="76">
-        <v>0</v>
-      </c>
-      <c r="H38" s="77">
-        <f>IF(AND($G38 &gt; 0, $E38 &gt; 0), CEILING(FV($G38, $E38-userAge, 0, -$F38, 1), 1000), $F38)</f>
+      <c r="G38" s="73">
+        <v>0</v>
+      </c>
+      <c r="H38" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7101,11 +7084,11 @@
       <c r="D39" s="11"/>
       <c r="E39" s="12"/>
       <c r="F39" s="13"/>
-      <c r="G39" s="76">
-        <v>0</v>
-      </c>
-      <c r="H39" s="77">
-        <f>IF(AND($G39 &gt; 0, $E39 &gt; 0), CEILING(FV($G39, $E39-userAge, 0, -$F39, 1), 1000), $F39)</f>
+      <c r="G39" s="73">
+        <v>0</v>
+      </c>
+      <c r="H39" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7113,11 +7096,11 @@
       <c r="D40" s="11"/>
       <c r="E40" s="12"/>
       <c r="F40" s="13"/>
-      <c r="G40" s="76">
-        <v>0</v>
-      </c>
-      <c r="H40" s="77">
-        <f>IF(AND($G40 &gt; 0, $E40 &gt; 0), CEILING(FV($G40, $E40-userAge, 0, -$F40, 1), 1000), $F40)</f>
+      <c r="G40" s="73">
+        <v>0</v>
+      </c>
+      <c r="H40" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7125,11 +7108,11 @@
       <c r="D41" s="11"/>
       <c r="E41" s="12"/>
       <c r="F41" s="13"/>
-      <c r="G41" s="76">
-        <v>0</v>
-      </c>
-      <c r="H41" s="77">
-        <f>IF(AND($G41 &gt; 0, $E41 &gt; 0), CEILING(FV($G41, $E41-userAge, 0, -$F41, 1), 1000), $F41)</f>
+      <c r="G41" s="73">
+        <v>0</v>
+      </c>
+      <c r="H41" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7137,11 +7120,11 @@
       <c r="D42" s="11"/>
       <c r="E42" s="12"/>
       <c r="F42" s="13"/>
-      <c r="G42" s="76">
-        <v>0</v>
-      </c>
-      <c r="H42" s="77">
-        <f>IF(AND($G42 &gt; 0, $E42 &gt; 0), CEILING(FV($G42, $E42-userAge, 0, -$F42, 1), 1000), $F42)</f>
+      <c r="G42" s="73">
+        <v>0</v>
+      </c>
+      <c r="H42" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7149,11 +7132,11 @@
       <c r="D43" s="11"/>
       <c r="E43" s="12"/>
       <c r="F43" s="13"/>
-      <c r="G43" s="76">
-        <v>0</v>
-      </c>
-      <c r="H43" s="77">
-        <f>IF(AND($G43 &gt; 0, $E43 &gt; 0), CEILING(FV($G43, $E43-userAge, 0, -$F43, 1), 1000), $F43)</f>
+      <c r="G43" s="73">
+        <v>0</v>
+      </c>
+      <c r="H43" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7161,11 +7144,11 @@
       <c r="D44" s="11"/>
       <c r="E44" s="12"/>
       <c r="F44" s="13"/>
-      <c r="G44" s="76">
-        <v>0</v>
-      </c>
-      <c r="H44" s="77">
-        <f>IF(AND($G44 &gt; 0, $E44 &gt; 0), CEILING(FV($G44, $E44-userAge, 0, -$F44, 1), 1000), $F44)</f>
+      <c r="G44" s="73">
+        <v>0</v>
+      </c>
+      <c r="H44" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7173,11 +7156,11 @@
       <c r="D45" s="11"/>
       <c r="E45" s="12"/>
       <c r="F45" s="13"/>
-      <c r="G45" s="76">
-        <v>0</v>
-      </c>
-      <c r="H45" s="77">
-        <f>IF(AND($G45 &gt; 0, $E45 &gt; 0), CEILING(FV($G45, $E45-userAge, 0, -$F45, 1), 1000), $F45)</f>
+      <c r="G45" s="73">
+        <v>0</v>
+      </c>
+      <c r="H45" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7185,11 +7168,11 @@
       <c r="D46" s="11"/>
       <c r="E46" s="12"/>
       <c r="F46" s="13"/>
-      <c r="G46" s="76">
-        <v>0</v>
-      </c>
-      <c r="H46" s="77">
-        <f>IF(AND($G46 &gt; 0, $E46 &gt; 0), CEILING(FV($G46, $E46-userAge, 0, -$F46, 1), 1000), $F46)</f>
+      <c r="G46" s="73">
+        <v>0</v>
+      </c>
+      <c r="H46" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7197,11 +7180,11 @@
       <c r="D47" s="11"/>
       <c r="E47" s="12"/>
       <c r="F47" s="13"/>
-      <c r="G47" s="76">
-        <v>0</v>
-      </c>
-      <c r="H47" s="77">
-        <f>IF(AND($G47 &gt; 0, $E47 &gt; 0), CEILING(FV($G47, $E47-userAge, 0, -$F47, 1), 1000), $F47)</f>
+      <c r="G47" s="73">
+        <v>0</v>
+      </c>
+      <c r="H47" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7209,11 +7192,11 @@
       <c r="D48" s="11"/>
       <c r="E48" s="12"/>
       <c r="F48" s="13"/>
-      <c r="G48" s="76">
-        <v>0</v>
-      </c>
-      <c r="H48" s="77">
-        <f>IF(AND($G48 &gt; 0, $E48 &gt; 0), CEILING(FV($G48, $E48-userAge, 0, -$F48, 1), 1000), $F48)</f>
+      <c r="G48" s="73">
+        <v>0</v>
+      </c>
+      <c r="H48" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7221,11 +7204,11 @@
       <c r="D49" s="11"/>
       <c r="E49" s="12"/>
       <c r="F49" s="13"/>
-      <c r="G49" s="76">
-        <v>0</v>
-      </c>
-      <c r="H49" s="77">
-        <f>IF(AND($G49 &gt; 0, $E49 &gt; 0), CEILING(FV($G49, $E49-userAge, 0, -$F49, 1), 1000), $F49)</f>
+      <c r="G49" s="73">
+        <v>0</v>
+      </c>
+      <c r="H49" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7233,11 +7216,11 @@
       <c r="D50" s="11"/>
       <c r="E50" s="12"/>
       <c r="F50" s="13"/>
-      <c r="G50" s="76">
-        <v>0</v>
-      </c>
-      <c r="H50" s="77">
-        <f>IF(AND($G50 &gt; 0, $E50 &gt; 0), CEILING(FV($G50, $E50-userAge, 0, -$F50, 1), 1000), $F50)</f>
+      <c r="G50" s="73">
+        <v>0</v>
+      </c>
+      <c r="H50" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7245,11 +7228,11 @@
       <c r="D51" s="11"/>
       <c r="E51" s="12"/>
       <c r="F51" s="13"/>
-      <c r="G51" s="76">
-        <v>0</v>
-      </c>
-      <c r="H51" s="77">
-        <f>IF(AND($G51 &gt; 0, $E51 &gt; 0), CEILING(FV($G51, $E51-userAge, 0, -$F51, 1), 1000), $F51)</f>
+      <c r="G51" s="73">
+        <v>0</v>
+      </c>
+      <c r="H51" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7257,11 +7240,11 @@
       <c r="D52" s="11"/>
       <c r="E52" s="12"/>
       <c r="F52" s="13"/>
-      <c r="G52" s="76">
-        <v>0</v>
-      </c>
-      <c r="H52" s="77">
-        <f>IF(AND($G52 &gt; 0, $E52 &gt; 0), CEILING(FV($G52, $E52-userAge, 0, -$F52, 1), 1000), $F52)</f>
+      <c r="G52" s="73">
+        <v>0</v>
+      </c>
+      <c r="H52" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7269,11 +7252,11 @@
       <c r="D53" s="11"/>
       <c r="E53" s="12"/>
       <c r="F53" s="13"/>
-      <c r="G53" s="76">
-        <v>0</v>
-      </c>
-      <c r="H53" s="77">
-        <f>IF(AND($G53 &gt; 0, $E53 &gt; 0), CEILING(FV($G53, $E53-userAge, 0, -$F53, 1), 1000), $F53)</f>
+      <c r="G53" s="73">
+        <v>0</v>
+      </c>
+      <c r="H53" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7281,11 +7264,11 @@
       <c r="D54" s="11"/>
       <c r="E54" s="12"/>
       <c r="F54" s="13"/>
-      <c r="G54" s="76">
-        <v>0</v>
-      </c>
-      <c r="H54" s="77">
-        <f>IF(AND($G54 &gt; 0, $E54 &gt; 0), CEILING(FV($G54, $E54-userAge, 0, -$F54, 1), 1000), $F54)</f>
+      <c r="G54" s="73">
+        <v>0</v>
+      </c>
+      <c r="H54" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7293,11 +7276,11 @@
       <c r="D55" s="11"/>
       <c r="E55" s="12"/>
       <c r="F55" s="13"/>
-      <c r="G55" s="76">
-        <v>0</v>
-      </c>
-      <c r="H55" s="77">
-        <f>IF(AND($G55 &gt; 0, $E55 &gt; 0), CEILING(FV($G55, $E55-userAge, 0, -$F55, 1), 1000), $F55)</f>
+      <c r="G55" s="73">
+        <v>0</v>
+      </c>
+      <c r="H55" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7305,11 +7288,11 @@
       <c r="D56" s="11"/>
       <c r="E56" s="12"/>
       <c r="F56" s="13"/>
-      <c r="G56" s="76">
-        <v>0</v>
-      </c>
-      <c r="H56" s="77">
-        <f>IF(AND($G56 &gt; 0, $E56 &gt; 0), CEILING(FV($G56, $E56-userAge, 0, -$F56, 1), 1000), $F56)</f>
+      <c r="G56" s="73">
+        <v>0</v>
+      </c>
+      <c r="H56" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7317,11 +7300,11 @@
       <c r="D57" s="11"/>
       <c r="E57" s="12"/>
       <c r="F57" s="13"/>
-      <c r="G57" s="76">
-        <v>0</v>
-      </c>
-      <c r="H57" s="77">
-        <f>IF(AND($G57 &gt; 0, $E57 &gt; 0), CEILING(FV($G57, $E57-userAge, 0, -$F57, 1), 1000), $F57)</f>
+      <c r="G57" s="73">
+        <v>0</v>
+      </c>
+      <c r="H57" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7329,11 +7312,11 @@
       <c r="D58" s="11"/>
       <c r="E58" s="12"/>
       <c r="F58" s="13"/>
-      <c r="G58" s="76">
-        <v>0</v>
-      </c>
-      <c r="H58" s="77">
-        <f>IF(AND($G58 &gt; 0, $E58 &gt; 0), CEILING(FV($G58, $E58-userAge, 0, -$F58, 1), 1000), $F58)</f>
+      <c r="G58" s="73">
+        <v>0</v>
+      </c>
+      <c r="H58" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7341,11 +7324,11 @@
       <c r="D59" s="11"/>
       <c r="E59" s="12"/>
       <c r="F59" s="13"/>
-      <c r="G59" s="76">
-        <v>0</v>
-      </c>
-      <c r="H59" s="77">
-        <f>IF(AND($G59 &gt; 0, $E59 &gt; 0), CEILING(FV($G59, $E59-userAge, 0, -$F59, 1), 1000), $F59)</f>
+      <c r="G59" s="73">
+        <v>0</v>
+      </c>
+      <c r="H59" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7353,11 +7336,11 @@
       <c r="D60" s="11"/>
       <c r="E60" s="12"/>
       <c r="F60" s="13"/>
-      <c r="G60" s="76">
-        <v>0</v>
-      </c>
-      <c r="H60" s="77">
-        <f>IF(AND($G60 &gt; 0, $E60 &gt; 0), CEILING(FV($G60, $E60-userAge, 0, -$F60, 1), 1000), $F60)</f>
+      <c r="G60" s="73">
+        <v>0</v>
+      </c>
+      <c r="H60" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7365,11 +7348,11 @@
       <c r="D61" s="11"/>
       <c r="E61" s="12"/>
       <c r="F61" s="13"/>
-      <c r="G61" s="76">
-        <v>0</v>
-      </c>
-      <c r="H61" s="77">
-        <f>IF(AND($G61 &gt; 0, $E61 &gt; 0), CEILING(FV($G61, $E61-userAge, 0, -$F61, 1), 1000), $F61)</f>
+      <c r="G61" s="73">
+        <v>0</v>
+      </c>
+      <c r="H61" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7377,11 +7360,11 @@
       <c r="D62" s="11"/>
       <c r="E62" s="12"/>
       <c r="F62" s="13"/>
-      <c r="G62" s="76">
-        <v>0</v>
-      </c>
-      <c r="H62" s="77">
-        <f>IF(AND($G62 &gt; 0, $E62 &gt; 0), CEILING(FV($G62, $E62-userAge, 0, -$F62, 1), 1000), $F62)</f>
+      <c r="G62" s="73">
+        <v>0</v>
+      </c>
+      <c r="H62" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7389,11 +7372,11 @@
       <c r="D63" s="11"/>
       <c r="E63" s="12"/>
       <c r="F63" s="13"/>
-      <c r="G63" s="76">
-        <v>0</v>
-      </c>
-      <c r="H63" s="77">
-        <f>IF(AND($G63 &gt; 0, $E63 &gt; 0), CEILING(FV($G63, $E63-userAge, 0, -$F63, 1), 1000), $F63)</f>
+      <c r="G63" s="73">
+        <v>0</v>
+      </c>
+      <c r="H63" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7401,11 +7384,11 @@
       <c r="D64" s="11"/>
       <c r="E64" s="12"/>
       <c r="F64" s="13"/>
-      <c r="G64" s="76">
-        <v>0</v>
-      </c>
-      <c r="H64" s="77">
-        <f>IF(AND($G64 &gt; 0, $E64 &gt; 0), CEILING(FV($G64, $E64-userAge, 0, -$F64, 1), 1000), $F64)</f>
+      <c r="G64" s="73">
+        <v>0</v>
+      </c>
+      <c r="H64" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7413,11 +7396,11 @@
       <c r="D65" s="11"/>
       <c r="E65" s="12"/>
       <c r="F65" s="13"/>
-      <c r="G65" s="76">
-        <v>0</v>
-      </c>
-      <c r="H65" s="77">
-        <f>IF(AND($G65 &gt; 0, $E65 &gt; 0), CEILING(FV($G65, $E65-userAge, 0, -$F65, 1), 1000), $F65)</f>
+      <c r="G65" s="73">
+        <v>0</v>
+      </c>
+      <c r="H65" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7425,11 +7408,11 @@
       <c r="D66" s="11"/>
       <c r="E66" s="12"/>
       <c r="F66" s="13"/>
-      <c r="G66" s="76">
-        <v>0</v>
-      </c>
-      <c r="H66" s="77">
-        <f>IF(AND($G66 &gt; 0, $E66 &gt; 0), CEILING(FV($G66, $E66-userAge, 0, -$F66, 1), 1000), $F66)</f>
+      <c r="G66" s="73">
+        <v>0</v>
+      </c>
+      <c r="H66" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7437,11 +7420,11 @@
       <c r="D67" s="11"/>
       <c r="E67" s="12"/>
       <c r="F67" s="13"/>
-      <c r="G67" s="76">
-        <v>0</v>
-      </c>
-      <c r="H67" s="77">
-        <f>IF(AND($G67 &gt; 0, $E67 &gt; 0), CEILING(FV($G67, $E67-userAge, 0, -$F67, 1), 1000), $F67)</f>
+      <c r="G67" s="73">
+        <v>0</v>
+      </c>
+      <c r="H67" s="74">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7449,11 +7432,11 @@
       <c r="D68" s="11"/>
       <c r="E68" s="12"/>
       <c r="F68" s="13"/>
-      <c r="G68" s="76">
-        <v>0</v>
-      </c>
-      <c r="H68" s="77">
-        <f>IF(AND($G68 &gt; 0, $E68 &gt; 0), CEILING(FV($G68, $E68-userAge, 0, -$F68, 1), 1000), $F68)</f>
+      <c r="G68" s="73">
+        <v>0</v>
+      </c>
+      <c r="H68" s="74">
+        <f t="shared" ref="H68:H99" si="2">IF(AND($G68 &gt; 0, $E68 &gt; 0), CEILING(FV($G68, $E68-userAge, 0, -$F68, 1), 1000), $F68)</f>
         <v>0</v>
       </c>
     </row>
@@ -7461,11 +7444,11 @@
       <c r="D69" s="11"/>
       <c r="E69" s="12"/>
       <c r="F69" s="13"/>
-      <c r="G69" s="76">
-        <v>0</v>
-      </c>
-      <c r="H69" s="77">
-        <f>IF(AND($G69 &gt; 0, $E69 &gt; 0), CEILING(FV($G69, $E69-userAge, 0, -$F69, 1), 1000), $F69)</f>
+      <c r="G69" s="73">
+        <v>0</v>
+      </c>
+      <c r="H69" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7473,11 +7456,11 @@
       <c r="D70" s="11"/>
       <c r="E70" s="12"/>
       <c r="F70" s="13"/>
-      <c r="G70" s="76">
-        <v>0</v>
-      </c>
-      <c r="H70" s="77">
-        <f>IF(AND($G70 &gt; 0, $E70 &gt; 0), CEILING(FV($G70, $E70-userAge, 0, -$F70, 1), 1000), $F70)</f>
+      <c r="G70" s="73">
+        <v>0</v>
+      </c>
+      <c r="H70" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7485,11 +7468,11 @@
       <c r="D71" s="11"/>
       <c r="E71" s="12"/>
       <c r="F71" s="13"/>
-      <c r="G71" s="76">
-        <v>0</v>
-      </c>
-      <c r="H71" s="77">
-        <f>IF(AND($G71 &gt; 0, $E71 &gt; 0), CEILING(FV($G71, $E71-userAge, 0, -$F71, 1), 1000), $F71)</f>
+      <c r="G71" s="73">
+        <v>0</v>
+      </c>
+      <c r="H71" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7497,11 +7480,11 @@
       <c r="D72" s="11"/>
       <c r="E72" s="12"/>
       <c r="F72" s="13"/>
-      <c r="G72" s="76">
-        <v>0</v>
-      </c>
-      <c r="H72" s="77">
-        <f>IF(AND($G72 &gt; 0, $E72 &gt; 0), CEILING(FV($G72, $E72-userAge, 0, -$F72, 1), 1000), $F72)</f>
+      <c r="G72" s="73">
+        <v>0</v>
+      </c>
+      <c r="H72" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7509,11 +7492,11 @@
       <c r="D73" s="11"/>
       <c r="E73" s="12"/>
       <c r="F73" s="13"/>
-      <c r="G73" s="76">
-        <v>0</v>
-      </c>
-      <c r="H73" s="77">
-        <f>IF(AND($G73 &gt; 0, $E73 &gt; 0), CEILING(FV($G73, $E73-userAge, 0, -$F73, 1), 1000), $F73)</f>
+      <c r="G73" s="73">
+        <v>0</v>
+      </c>
+      <c r="H73" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7521,11 +7504,11 @@
       <c r="D74" s="11"/>
       <c r="E74" s="12"/>
       <c r="F74" s="13"/>
-      <c r="G74" s="76">
-        <v>0</v>
-      </c>
-      <c r="H74" s="77">
-        <f>IF(AND($G74 &gt; 0, $E74 &gt; 0), CEILING(FV($G74, $E74-userAge, 0, -$F74, 1), 1000), $F74)</f>
+      <c r="G74" s="73">
+        <v>0</v>
+      </c>
+      <c r="H74" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7533,11 +7516,11 @@
       <c r="D75" s="11"/>
       <c r="E75" s="12"/>
       <c r="F75" s="13"/>
-      <c r="G75" s="76">
-        <v>0</v>
-      </c>
-      <c r="H75" s="77">
-        <f>IF(AND($G75 &gt; 0, $E75 &gt; 0), CEILING(FV($G75, $E75-userAge, 0, -$F75, 1), 1000), $F75)</f>
+      <c r="G75" s="73">
+        <v>0</v>
+      </c>
+      <c r="H75" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7545,11 +7528,11 @@
       <c r="D76" s="11"/>
       <c r="E76" s="12"/>
       <c r="F76" s="13"/>
-      <c r="G76" s="76">
-        <v>0</v>
-      </c>
-      <c r="H76" s="77">
-        <f>IF(AND($G76 &gt; 0, $E76 &gt; 0), CEILING(FV($G76, $E76-userAge, 0, -$F76, 1), 1000), $F76)</f>
+      <c r="G76" s="73">
+        <v>0</v>
+      </c>
+      <c r="H76" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7557,11 +7540,11 @@
       <c r="D77" s="11"/>
       <c r="E77" s="12"/>
       <c r="F77" s="13"/>
-      <c r="G77" s="76">
-        <v>0</v>
-      </c>
-      <c r="H77" s="77">
-        <f>IF(AND($G77 &gt; 0, $E77 &gt; 0), CEILING(FV($G77, $E77-userAge, 0, -$F77, 1), 1000), $F77)</f>
+      <c r="G77" s="73">
+        <v>0</v>
+      </c>
+      <c r="H77" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7569,11 +7552,11 @@
       <c r="D78" s="11"/>
       <c r="E78" s="12"/>
       <c r="F78" s="13"/>
-      <c r="G78" s="76">
-        <v>0</v>
-      </c>
-      <c r="H78" s="77">
-        <f>IF(AND($G78 &gt; 0, $E78 &gt; 0), CEILING(FV($G78, $E78-userAge, 0, -$F78, 1), 1000), $F78)</f>
+      <c r="G78" s="73">
+        <v>0</v>
+      </c>
+      <c r="H78" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7581,11 +7564,11 @@
       <c r="D79" s="11"/>
       <c r="E79" s="12"/>
       <c r="F79" s="13"/>
-      <c r="G79" s="76">
-        <v>0</v>
-      </c>
-      <c r="H79" s="77">
-        <f>IF(AND($G79 &gt; 0, $E79 &gt; 0), CEILING(FV($G79, $E79-userAge, 0, -$F79, 1), 1000), $F79)</f>
+      <c r="G79" s="73">
+        <v>0</v>
+      </c>
+      <c r="H79" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7593,11 +7576,11 @@
       <c r="D80" s="11"/>
       <c r="E80" s="12"/>
       <c r="F80" s="13"/>
-      <c r="G80" s="76">
-        <v>0</v>
-      </c>
-      <c r="H80" s="77">
-        <f>IF(AND($G80 &gt; 0, $E80 &gt; 0), CEILING(FV($G80, $E80-userAge, 0, -$F80, 1), 1000), $F80)</f>
+      <c r="G80" s="73">
+        <v>0</v>
+      </c>
+      <c r="H80" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7605,11 +7588,11 @@
       <c r="D81" s="11"/>
       <c r="E81" s="12"/>
       <c r="F81" s="13"/>
-      <c r="G81" s="76">
-        <v>0</v>
-      </c>
-      <c r="H81" s="77">
-        <f>IF(AND($G81 &gt; 0, $E81 &gt; 0), CEILING(FV($G81, $E81-userAge, 0, -$F81, 1), 1000), $F81)</f>
+      <c r="G81" s="73">
+        <v>0</v>
+      </c>
+      <c r="H81" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7617,11 +7600,11 @@
       <c r="D82" s="11"/>
       <c r="E82" s="12"/>
       <c r="F82" s="13"/>
-      <c r="G82" s="76">
-        <v>0</v>
-      </c>
-      <c r="H82" s="77">
-        <f>IF(AND($G82 &gt; 0, $E82 &gt; 0), CEILING(FV($G82, $E82-userAge, 0, -$F82, 1), 1000), $F82)</f>
+      <c r="G82" s="73">
+        <v>0</v>
+      </c>
+      <c r="H82" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7629,11 +7612,11 @@
       <c r="D83" s="11"/>
       <c r="E83" s="12"/>
       <c r="F83" s="13"/>
-      <c r="G83" s="76">
-        <v>0</v>
-      </c>
-      <c r="H83" s="77">
-        <f>IF(AND($G83 &gt; 0, $E83 &gt; 0), CEILING(FV($G83, $E83-userAge, 0, -$F83, 1), 1000), $F83)</f>
+      <c r="G83" s="73">
+        <v>0</v>
+      </c>
+      <c r="H83" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7641,11 +7624,11 @@
       <c r="D84" s="11"/>
       <c r="E84" s="12"/>
       <c r="F84" s="13"/>
-      <c r="G84" s="76">
-        <v>0</v>
-      </c>
-      <c r="H84" s="77">
-        <f>IF(AND($G84 &gt; 0, $E84 &gt; 0), CEILING(FV($G84, $E84-userAge, 0, -$F84, 1), 1000), $F84)</f>
+      <c r="G84" s="73">
+        <v>0</v>
+      </c>
+      <c r="H84" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7653,11 +7636,11 @@
       <c r="D85" s="11"/>
       <c r="E85" s="12"/>
       <c r="F85" s="13"/>
-      <c r="G85" s="76">
-        <v>0</v>
-      </c>
-      <c r="H85" s="77">
-        <f>IF(AND($G85 &gt; 0, $E85 &gt; 0), CEILING(FV($G85, $E85-userAge, 0, -$F85, 1), 1000), $F85)</f>
+      <c r="G85" s="73">
+        <v>0</v>
+      </c>
+      <c r="H85" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7665,11 +7648,11 @@
       <c r="D86" s="11"/>
       <c r="E86" s="12"/>
       <c r="F86" s="13"/>
-      <c r="G86" s="76">
-        <v>0</v>
-      </c>
-      <c r="H86" s="77">
-        <f>IF(AND($G86 &gt; 0, $E86 &gt; 0), CEILING(FV($G86, $E86-userAge, 0, -$F86, 1), 1000), $F86)</f>
+      <c r="G86" s="73">
+        <v>0</v>
+      </c>
+      <c r="H86" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7677,11 +7660,11 @@
       <c r="D87" s="11"/>
       <c r="E87" s="12"/>
       <c r="F87" s="13"/>
-      <c r="G87" s="76">
-        <v>0</v>
-      </c>
-      <c r="H87" s="77">
-        <f>IF(AND($G87 &gt; 0, $E87 &gt; 0), CEILING(FV($G87, $E87-userAge, 0, -$F87, 1), 1000), $F87)</f>
+      <c r="G87" s="73">
+        <v>0</v>
+      </c>
+      <c r="H87" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7689,11 +7672,11 @@
       <c r="D88" s="11"/>
       <c r="E88" s="12"/>
       <c r="F88" s="13"/>
-      <c r="G88" s="76">
-        <v>0</v>
-      </c>
-      <c r="H88" s="77">
-        <f>IF(AND($G88 &gt; 0, $E88 &gt; 0), CEILING(FV($G88, $E88-userAge, 0, -$F88, 1), 1000), $F88)</f>
+      <c r="G88" s="73">
+        <v>0</v>
+      </c>
+      <c r="H88" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7701,11 +7684,11 @@
       <c r="D89" s="11"/>
       <c r="E89" s="12"/>
       <c r="F89" s="13"/>
-      <c r="G89" s="76">
-        <v>0</v>
-      </c>
-      <c r="H89" s="77">
-        <f>IF(AND($G89 &gt; 0, $E89 &gt; 0), CEILING(FV($G89, $E89-userAge, 0, -$F89, 1), 1000), $F89)</f>
+      <c r="G89" s="73">
+        <v>0</v>
+      </c>
+      <c r="H89" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7713,11 +7696,11 @@
       <c r="D90" s="11"/>
       <c r="E90" s="12"/>
       <c r="F90" s="13"/>
-      <c r="G90" s="76">
-        <v>0</v>
-      </c>
-      <c r="H90" s="77">
-        <f>IF(AND($G90 &gt; 0, $E90 &gt; 0), CEILING(FV($G90, $E90-userAge, 0, -$F90, 1), 1000), $F90)</f>
+      <c r="G90" s="73">
+        <v>0</v>
+      </c>
+      <c r="H90" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7725,11 +7708,11 @@
       <c r="D91" s="11"/>
       <c r="E91" s="12"/>
       <c r="F91" s="13"/>
-      <c r="G91" s="76">
-        <v>0</v>
-      </c>
-      <c r="H91" s="77">
-        <f>IF(AND($G91 &gt; 0, $E91 &gt; 0), CEILING(FV($G91, $E91-userAge, 0, -$F91, 1), 1000), $F91)</f>
+      <c r="G91" s="73">
+        <v>0</v>
+      </c>
+      <c r="H91" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7737,11 +7720,11 @@
       <c r="D92" s="11"/>
       <c r="E92" s="12"/>
       <c r="F92" s="13"/>
-      <c r="G92" s="76">
-        <v>0</v>
-      </c>
-      <c r="H92" s="77">
-        <f>IF(AND($G92 &gt; 0, $E92 &gt; 0), CEILING(FV($G92, $E92-userAge, 0, -$F92, 1), 1000), $F92)</f>
+      <c r="G92" s="73">
+        <v>0</v>
+      </c>
+      <c r="H92" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7749,11 +7732,11 @@
       <c r="D93" s="11"/>
       <c r="E93" s="12"/>
       <c r="F93" s="13"/>
-      <c r="G93" s="76">
-        <v>0</v>
-      </c>
-      <c r="H93" s="77">
-        <f>IF(AND($G93 &gt; 0, $E93 &gt; 0), CEILING(FV($G93, $E93-userAge, 0, -$F93, 1), 1000), $F93)</f>
+      <c r="G93" s="73">
+        <v>0</v>
+      </c>
+      <c r="H93" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7761,11 +7744,11 @@
       <c r="D94" s="11"/>
       <c r="E94" s="12"/>
       <c r="F94" s="13"/>
-      <c r="G94" s="76">
-        <v>0</v>
-      </c>
-      <c r="H94" s="77">
-        <f>IF(AND($G94 &gt; 0, $E94 &gt; 0), CEILING(FV($G94, $E94-userAge, 0, -$F94, 1), 1000), $F94)</f>
+      <c r="G94" s="73">
+        <v>0</v>
+      </c>
+      <c r="H94" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7773,11 +7756,11 @@
       <c r="D95" s="11"/>
       <c r="E95" s="12"/>
       <c r="F95" s="13"/>
-      <c r="G95" s="76">
-        <v>0</v>
-      </c>
-      <c r="H95" s="77">
-        <f>IF(AND($G95 &gt; 0, $E95 &gt; 0), CEILING(FV($G95, $E95-userAge, 0, -$F95, 1), 1000), $F95)</f>
+      <c r="G95" s="73">
+        <v>0</v>
+      </c>
+      <c r="H95" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7785,11 +7768,11 @@
       <c r="D96" s="11"/>
       <c r="E96" s="12"/>
       <c r="F96" s="13"/>
-      <c r="G96" s="76">
-        <v>0</v>
-      </c>
-      <c r="H96" s="77">
-        <f>IF(AND($G96 &gt; 0, $E96 &gt; 0), CEILING(FV($G96, $E96-userAge, 0, -$F96, 1), 1000), $F96)</f>
+      <c r="G96" s="73">
+        <v>0</v>
+      </c>
+      <c r="H96" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7797,11 +7780,11 @@
       <c r="D97" s="11"/>
       <c r="E97" s="12"/>
       <c r="F97" s="13"/>
-      <c r="G97" s="76">
-        <v>0</v>
-      </c>
-      <c r="H97" s="77">
-        <f>IF(AND($G97 &gt; 0, $E97 &gt; 0), CEILING(FV($G97, $E97-userAge, 0, -$F97, 1), 1000), $F97)</f>
+      <c r="G97" s="73">
+        <v>0</v>
+      </c>
+      <c r="H97" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7809,11 +7792,11 @@
       <c r="D98" s="11"/>
       <c r="E98" s="12"/>
       <c r="F98" s="13"/>
-      <c r="G98" s="76">
-        <v>0</v>
-      </c>
-      <c r="H98" s="77">
-        <f>IF(AND($G98 &gt; 0, $E98 &gt; 0), CEILING(FV($G98, $E98-userAge, 0, -$F98, 1), 1000), $F98)</f>
+      <c r="G98" s="73">
+        <v>0</v>
+      </c>
+      <c r="H98" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7821,11 +7804,11 @@
       <c r="D99" s="11"/>
       <c r="E99" s="12"/>
       <c r="F99" s="13"/>
-      <c r="G99" s="76">
-        <v>0</v>
-      </c>
-      <c r="H99" s="77">
-        <f>IF(AND($G99 &gt; 0, $E99 &gt; 0), CEILING(FV($G99, $E99-userAge, 0, -$F99, 1), 1000), $F99)</f>
+      <c r="G99" s="73">
+        <v>0</v>
+      </c>
+      <c r="H99" s="74">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7833,11 +7816,11 @@
       <c r="D100" s="11"/>
       <c r="E100" s="12"/>
       <c r="F100" s="13"/>
-      <c r="G100" s="76">
-        <v>0</v>
-      </c>
-      <c r="H100" s="77">
-        <f>IF(AND($G100 &gt; 0, $E100 &gt; 0), CEILING(FV($G100, $E100-userAge, 0, -$F100, 1), 1000), $F100)</f>
+      <c r="G100" s="73">
+        <v>0</v>
+      </c>
+      <c r="H100" s="74">
+        <f t="shared" ref="H100:H106" si="3">IF(AND($G100 &gt; 0, $E100 &gt; 0), CEILING(FV($G100, $E100-userAge, 0, -$F100, 1), 1000), $F100)</f>
         <v>0</v>
       </c>
     </row>
@@ -7846,17 +7829,17 @@
         <v>54</v>
       </c>
       <c r="E101" s="12">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F101" s="13">
-        <v>-100000</v>
-      </c>
-      <c r="G101" s="76">
-        <v>0</v>
-      </c>
-      <c r="H101" s="77">
-        <f>IF(AND($G101 &gt; 0, $E101 &gt; 0), CEILING(FV($G101, $E101-userAge, 0, -$F101, 1), 1000), $F101)</f>
-        <v>-100000</v>
+        <v>-1000000</v>
+      </c>
+      <c r="G101" s="73">
+        <v>0</v>
+      </c>
+      <c r="H101" s="74">
+        <f t="shared" si="3"/>
+        <v>-1000000</v>
       </c>
     </row>
     <row r="102" spans="4:8" x14ac:dyDescent="0.25">
@@ -7864,14 +7847,14 @@
         <v>57</v>
       </c>
       <c r="E102" s="12">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F102" s="13"/>
-      <c r="G102" s="76">
-        <v>0</v>
-      </c>
-      <c r="H102" s="77">
-        <f>IF(AND($G102 &gt; 0, $E102 &gt; 0), CEILING(FV($G102, $E102-userAge, 0, -$F102, 1), 1000), $F102)</f>
+      <c r="G102" s="73">
+        <v>0</v>
+      </c>
+      <c r="H102" s="74">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7881,16 +7864,16 @@
       </c>
       <c r="E103" s="71">
         <f>userRetirementAge</f>
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F103" s="13">
         <v>-2000000</v>
       </c>
-      <c r="G103" s="76">
-        <v>0</v>
-      </c>
-      <c r="H103" s="77">
-        <f>IF(AND($G103 &gt; 0, $E103 &gt; 0), CEILING(FV($G103, $E103-userAge, 0, -$F103, 1), 1000), $F103)</f>
+      <c r="G103" s="73">
+        <v>0</v>
+      </c>
+      <c r="H103" s="74">
+        <f t="shared" si="3"/>
         <v>-2000000</v>
       </c>
     </row>
@@ -7905,11 +7888,11 @@
       <c r="F104" s="25">
         <v>-10000000</v>
       </c>
-      <c r="G104" s="78">
-        <v>0</v>
-      </c>
-      <c r="H104" s="79">
-        <f>IF(AND($G104 &gt; 0, $E104 &gt; 0), CEILING(FV($G104, $E104-userAge, 0, -$F104, 1), 1000), $F104)</f>
+      <c r="G104" s="75">
+        <v>0</v>
+      </c>
+      <c r="H104" s="76">
+        <f t="shared" si="3"/>
         <v>-10000000</v>
       </c>
     </row>
@@ -7919,14 +7902,14 @@
       </c>
       <c r="E105" s="67">
         <f>userRetirementAge</f>
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F105" s="13"/>
-      <c r="G105" s="80">
-        <v>0</v>
-      </c>
-      <c r="H105" s="81">
-        <f>IF(AND($G105 &gt; 0, $E105 &gt; 0), CEILING(FV($G105, $E105-userAge, 0, -$F105, 1), 1000), $F105)</f>
+      <c r="G105" s="77">
+        <v>0</v>
+      </c>
+      <c r="H105" s="78">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7939,11 +7922,11 @@
         <v>80</v>
       </c>
       <c r="F106" s="70"/>
-      <c r="G106" s="78">
-        <v>0</v>
-      </c>
-      <c r="H106" s="79">
-        <f>IF(AND($G106 &gt; 0, $E106 &gt; 0), CEILING(FV($G106, $E106-userAge, 0, -$F106, 1), 1000), $F106)</f>
+      <c r="G106" s="75">
+        <v>0</v>
+      </c>
+      <c r="H106" s="76">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7981,14 +7964,14 @@
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="84" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="74"/>
-      <c r="D5" s="73" t="s">
+      <c r="B5" s="85"/>
+      <c r="D5" s="84" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="74"/>
+      <c r="E5" s="85"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
